--- a/PRODUCTION PLANNING.xlsx
+++ b/PRODUCTION PLANNING.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD910DF-4427-487A-845D-17E3939ECFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1264B8-54B9-4D7D-9CD9-8D58323551D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ELCEE!$A$2:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SEALAND!$A$2:$J$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SEALAND!$A$2:$J$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="549">
   <si>
     <t>ITEM</t>
   </si>
@@ -254,55 +254,1411 @@
     <t>R &amp; S</t>
   </si>
   <si>
-    <t>RSFGH2600024/          24.01.26</t>
-  </si>
-  <si>
-    <t>2 9/16 10M X 3"1502 FEMALE WECO</t>
-  </si>
-  <si>
-    <t>0750-01</t>
+    <t>120 DIA 4130</t>
+  </si>
+  <si>
+    <t>110 DIA 4130</t>
+  </si>
+  <si>
+    <t>200 RCS 4130</t>
+  </si>
+  <si>
+    <t>SEALAND</t>
+  </si>
+  <si>
+    <t>SCC-P18029/20.02.26</t>
+  </si>
+  <si>
+    <t>8"FIG 100/200/206 NUT WITH 3 X 150 SORF</t>
+  </si>
+  <si>
+    <t>0494/0083</t>
+  </si>
+  <si>
+    <t>160 RCS A105</t>
+  </si>
+  <si>
+    <t>6"FIG 100/200/206 NUT</t>
+  </si>
+  <si>
+    <t>0120</t>
+  </si>
+  <si>
+    <t>125 RCS A105</t>
+  </si>
+  <si>
+    <t>5"FIG 100/200/206 NUT</t>
+  </si>
+  <si>
+    <t>01100</t>
+  </si>
+  <si>
+    <t>130 RCS A105</t>
+  </si>
+  <si>
+    <t>100 DIA 4130</t>
+  </si>
+  <si>
+    <t>180 DIA 4130</t>
+  </si>
+  <si>
+    <t>CUTTING READY FOR FORGING</t>
+  </si>
+  <si>
+    <t>190 DIA 4130</t>
+  </si>
+  <si>
+    <t>0862</t>
+  </si>
+  <si>
+    <t>125 RCS 4130</t>
+  </si>
+  <si>
+    <t>INTEGRAL TEE 2"1502</t>
+  </si>
+  <si>
+    <t>4"FIG 100/200/206 NUT</t>
+  </si>
+  <si>
+    <t>0423</t>
+  </si>
+  <si>
+    <t>4"FIG 602/1002 NUT</t>
+  </si>
+  <si>
+    <t>5"FIG 1002 NUT</t>
+  </si>
+  <si>
+    <t>3"FIG 1502 NUT</t>
+  </si>
+  <si>
+    <t>4"FIG 1502 NUT</t>
+  </si>
+  <si>
+    <t>0511</t>
+  </si>
+  <si>
+    <t>0516</t>
+  </si>
+  <si>
+    <t>0498</t>
+  </si>
+  <si>
+    <t>0506</t>
+  </si>
+  <si>
+    <t>3"FIG 1502 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>3"FIG 1502 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0499</t>
+  </si>
+  <si>
+    <t>0500</t>
+  </si>
+  <si>
+    <t>80 DIA 4130</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0446</t>
+  </si>
+  <si>
+    <t>0447</t>
+  </si>
+  <si>
+    <t>1"FIG 200/206 NUT</t>
+  </si>
+  <si>
+    <t>1 1/4"FIG 200 NUT</t>
+  </si>
+  <si>
+    <t>1 1/2" FIG 200 NUT</t>
+  </si>
+  <si>
+    <t>2"FIG 100/200/206 NUT</t>
+  </si>
+  <si>
+    <t>2 1/2"FIG 100 NUT</t>
+  </si>
+  <si>
+    <t>3"FIG 100/200/206 NUT</t>
+  </si>
+  <si>
+    <t>0121</t>
+  </si>
+  <si>
+    <t>0119</t>
+  </si>
+  <si>
+    <t>0428</t>
+  </si>
+  <si>
+    <t>250pcs(1st shipment) WAIT FOR MATERIAL</t>
+  </si>
+  <si>
+    <t>20pcs(1st shipment) WAIT FOR MATERIAL</t>
+  </si>
+  <si>
+    <t>40pcs(1st shipment) WAIT FOR MATERIAL</t>
+  </si>
+  <si>
+    <t>30pcs(1st shipment) WAIT FOR MATERIAL</t>
+  </si>
+  <si>
+    <t>4"FIG 207 NUT</t>
+  </si>
+  <si>
+    <t>01271</t>
+  </si>
+  <si>
+    <t>1"FIG 602/1002 NUT</t>
+  </si>
+  <si>
+    <t>1 1/2"FIG 602 NUT</t>
+  </si>
+  <si>
+    <t>2"FIG 602 NUT</t>
+  </si>
+  <si>
+    <t>3"FIG 602/1002 NUT</t>
+  </si>
+  <si>
+    <t>0491</t>
+  </si>
+  <si>
+    <t>01093</t>
+  </si>
+  <si>
+    <t>0441</t>
+  </si>
+  <si>
+    <t>0488</t>
+  </si>
+  <si>
+    <t>370pcs(1st shipment) WAIT FOR MATERIAL</t>
+  </si>
+  <si>
+    <t>200pcs(1st shipment) WAIT FOR MATERIAL</t>
+  </si>
+  <si>
+    <t>2"FIG 2202 NUT</t>
+  </si>
+  <si>
+    <t>01064</t>
+  </si>
+  <si>
+    <t>3"FIG 2202 NUT</t>
+  </si>
+  <si>
+    <t>0492</t>
+  </si>
+  <si>
+    <t>0493</t>
+  </si>
+  <si>
+    <t>SELAND</t>
+  </si>
+  <si>
+    <t>70 DIA 4130</t>
+  </si>
+  <si>
+    <t>1.6/51MM</t>
+  </si>
+  <si>
+    <t>1.8/58MM</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 MALE PLUG</t>
+  </si>
+  <si>
+    <t>0774</t>
+  </si>
+  <si>
+    <t>50+50</t>
+  </si>
+  <si>
+    <t>6.5/106MM</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 FEMALE PLUG</t>
+  </si>
+  <si>
+    <t>0775</t>
+  </si>
+  <si>
+    <t>3"FIG 1502 MALE PLUG</t>
+  </si>
+  <si>
+    <t>0827</t>
+  </si>
+  <si>
+    <t>30+30</t>
+  </si>
+  <si>
+    <t>01296</t>
+  </si>
+  <si>
+    <t>25+25</t>
+  </si>
+  <si>
+    <t>3"FIG 602 MALE PLUG(DIE USE MF 0827)</t>
+  </si>
+  <si>
+    <t>4"FIG 602 MALE PLUG(DIE USE MF 0829)</t>
+  </si>
+  <si>
+    <t>01298</t>
+  </si>
+  <si>
+    <t>4"FIG 206 MALE PLUG(DIE USE MF 0829)</t>
+  </si>
+  <si>
+    <t>01302</t>
+  </si>
+  <si>
+    <t>3"FIG 1502 FEMALE PLUG</t>
+  </si>
+  <si>
+    <t>0828</t>
+  </si>
+  <si>
+    <t>3"FIG 602 FEMALE PLUG(P/MC STOCK 0828)</t>
+  </si>
+  <si>
+    <t>140 DIA 4130</t>
+  </si>
+  <si>
+    <t>01299</t>
+  </si>
+  <si>
+    <t>01303</t>
+  </si>
+  <si>
+    <t>5"FIG 1002 MALE PLUG</t>
+  </si>
+  <si>
+    <t>5"FIG 1002 FEMALE PLUG</t>
+  </si>
+  <si>
+    <t>01300</t>
+  </si>
+  <si>
+    <t>01301</t>
+  </si>
+  <si>
+    <t>22.15/97MM</t>
+  </si>
+  <si>
+    <t>1 1/2"FIG 602 MALE THREAD</t>
+  </si>
+  <si>
+    <t>1"FIG 602 FEMALE THREAD</t>
+  </si>
+  <si>
+    <t>1"FIG 602 MALE THREAD</t>
+  </si>
+  <si>
+    <t>1 1/2"FIG 602 FEMALE THREAD</t>
+  </si>
+  <si>
+    <t>0486</t>
+  </si>
+  <si>
+    <t>0487</t>
+  </si>
+  <si>
+    <t>0489</t>
+  </si>
+  <si>
+    <t>0490</t>
+  </si>
+  <si>
+    <t>4"FIG 602 MALE THREAD</t>
+  </si>
+  <si>
+    <t>4"FIG 602 FEMALE THREAD</t>
+  </si>
+  <si>
+    <t>01096</t>
+  </si>
+  <si>
+    <t>01097</t>
+  </si>
+  <si>
+    <t>1"FIG 1002 MALE THREAD</t>
+  </si>
+  <si>
+    <t>1"FIG 1002 FEMALE THREAD</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 MALE THREAD</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 FEMALE THREAD</t>
+  </si>
+  <si>
+    <t>0448</t>
+  </si>
+  <si>
+    <t>0449</t>
+  </si>
+  <si>
+    <t>20pcs(1st shipment)</t>
+  </si>
+  <si>
+    <t>200pcs(1st shipment)MATERIAL READY FOR CUTTING</t>
+  </si>
+  <si>
+    <t>20.4/98MM</t>
+  </si>
+  <si>
+    <t>7.2/96MM</t>
+  </si>
+  <si>
+    <t>CROSSOVER 2"1502 MALE X MALE</t>
+  </si>
+  <si>
+    <t>CROSSOVER 2"1502 MALE X FEMALE</t>
+  </si>
+  <si>
+    <t>0923</t>
+  </si>
+  <si>
+    <t>0931</t>
+  </si>
+  <si>
+    <t>25+15</t>
+  </si>
+  <si>
+    <t>8.0/160MM</t>
+  </si>
+  <si>
+    <t>12.0/160MM</t>
+  </si>
+  <si>
+    <t>CROSSOVER 2"1502 MALE X 3"1502 FEMALE</t>
+  </si>
+  <si>
+    <t>CROSSOVER 3"1502 MALE X 2"1502 FEMALE</t>
+  </si>
+  <si>
+    <t>0801</t>
+  </si>
+  <si>
+    <t>0800</t>
+  </si>
+  <si>
+    <t>CROSSOVER 2"1502 FEMALE X FEMALE</t>
+  </si>
+  <si>
+    <t>CROSSOVER 3"1502 MALE X MALE</t>
+  </si>
+  <si>
+    <t>0922</t>
+  </si>
+  <si>
+    <t>0967</t>
+  </si>
+  <si>
+    <t>16.5/185MM</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 'PLUG VALVE BODY</t>
+  </si>
+  <si>
+    <t>01304</t>
+  </si>
+  <si>
+    <t>80/90 DIA 4130</t>
+  </si>
+  <si>
+    <t>65 RCS A105</t>
+  </si>
+  <si>
+    <t>77 RCS A105</t>
+  </si>
+  <si>
+    <t>2"FIG 2202 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>2"FIG 2202 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>01280</t>
+  </si>
+  <si>
+    <t>01281</t>
+  </si>
+  <si>
+    <t>4.25/106MM</t>
+  </si>
+  <si>
+    <t>6.0/1069MM</t>
+  </si>
+  <si>
+    <t>95 DIA 4130</t>
+  </si>
+  <si>
+    <t>3"FIG 100/200/206 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0502</t>
+  </si>
+  <si>
+    <t>0503</t>
+  </si>
+  <si>
+    <t>3"FIG 100/200/206 MALE THRD</t>
+  </si>
+  <si>
+    <t>3"FIG 100/200/206 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>3"FIG 100/200/206 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>0429</t>
+  </si>
+  <si>
+    <t>0430</t>
+  </si>
+  <si>
+    <t>95pcs(1st shipment)FORGING OK,PENDING 130</t>
+  </si>
+  <si>
+    <t>155pcs(1st shipment)FORGING OK,PENDING 145</t>
+  </si>
+  <si>
+    <t>80pcs(1st shipment)FORGING OK,PENDING 120</t>
+  </si>
+  <si>
+    <t>40pcs FORGING OK,PENDING 210</t>
+  </si>
+  <si>
+    <t>4"FIG 100 MALE THRD</t>
+  </si>
+  <si>
+    <t>4"FIG 100 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>0426</t>
+  </si>
+  <si>
+    <t>0427</t>
+  </si>
+  <si>
+    <t>4"FIG 200/206 MALE B/W</t>
+  </si>
+  <si>
+    <t>4"FIG 200/206 FEMALE B/W</t>
+  </si>
+  <si>
+    <t>4"FIG 200/206 MALE THRD</t>
+  </si>
+  <si>
+    <t>4"FIG 200/206 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>0504</t>
+  </si>
+  <si>
+    <t>0505</t>
+  </si>
+  <si>
+    <t>0514</t>
+  </si>
+  <si>
+    <t>0515</t>
+  </si>
+  <si>
+    <t>5"FIG 100 MALE B/W</t>
+  </si>
+  <si>
+    <t>5"FIG 100 FEMALE B/W</t>
+  </si>
+  <si>
+    <t>5"FIG 100 MALE THRD</t>
+  </si>
+  <si>
+    <t>5"FIG 100 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>5"FIG 200/206 MALE THRD</t>
+  </si>
+  <si>
+    <t>5"FIG 200/206 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>6"FIG 100 MALE B/W</t>
+  </si>
+  <si>
+    <t>6"FIG 100 FEMALE B/W</t>
+  </si>
+  <si>
+    <t>6"FIG 200/206 MALE B/W</t>
+  </si>
+  <si>
+    <t>6"FIG 200/206 FEMALE B/W</t>
+  </si>
+  <si>
+    <t>6"FIG 100/200/206 MALE THRD</t>
+  </si>
+  <si>
+    <t>6"FIG 100/200/206 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>50+50+50</t>
+  </si>
+  <si>
+    <t>8"FIG 100/200 MALE B/W</t>
+  </si>
+  <si>
+    <t>8"FIG 100/200 FEMALE B/W</t>
+  </si>
+  <si>
+    <t>8"FIG 100/200/206 MALE THRD</t>
+  </si>
+  <si>
+    <t>8"FIG 100/200/206 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>50+50+25</t>
+  </si>
+  <si>
+    <t>BHEL-25328/17.02.26</t>
+  </si>
+  <si>
+    <t>3 1/8"-3000/5000PSI GATE</t>
+  </si>
+  <si>
+    <t>2 1/16"10000PSI VALVE BODY FBV</t>
+  </si>
+  <si>
+    <t>01276</t>
+  </si>
+  <si>
+    <t>01277</t>
+  </si>
+  <si>
+    <t>01273</t>
+  </si>
+  <si>
+    <t>BHEL</t>
+  </si>
+  <si>
+    <t>SS410</t>
+  </si>
+  <si>
+    <t>125 RCS'A105</t>
+  </si>
+  <si>
+    <t>01094-01</t>
+  </si>
+  <si>
+    <t>01095-01</t>
+  </si>
+  <si>
+    <t>01098-01</t>
+  </si>
+  <si>
+    <t>01099-01</t>
+  </si>
+  <si>
+    <t>1 1/4"FIG 200 MALE THRD</t>
+  </si>
+  <si>
+    <t>1 1/4"FIG 200 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>01286</t>
+  </si>
+  <si>
+    <t>01287</t>
+  </si>
+  <si>
+    <t>1 1/2" FIG 200 MALE THRD</t>
+  </si>
+  <si>
+    <t>01289</t>
+  </si>
+  <si>
+    <t>01290</t>
+  </si>
+  <si>
+    <t>1 1/2" FIG 200 MALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>1 1/2" FIG 200 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>1 1/2" FIG 200 FEMALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>1 1/2"FIG 602 MALE B/W SCH 160</t>
+  </si>
+  <si>
+    <t>1 1/2"FIG 602 FEMALE B/W SCH 160</t>
+  </si>
+  <si>
+    <t>01094</t>
+  </si>
+  <si>
+    <t>01095</t>
+  </si>
+  <si>
+    <t>2"FIG 602 MALE THRD</t>
+  </si>
+  <si>
+    <t>2"FIG 602 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>2"FIG 602 MALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>2"FIG 602 FEMALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>0442</t>
+  </si>
+  <si>
+    <t>100pcs(1st shipment)</t>
+  </si>
+  <si>
+    <t>3"FIG 602 MALE THRD</t>
+  </si>
+  <si>
+    <t>3"FIG 602 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>3"FIG 602 MALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>3"FIG 602 FEMALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>3"FIG 602 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>3"FIG 602 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0512</t>
+  </si>
+  <si>
+    <t>0513</t>
+  </si>
+  <si>
+    <t>3"FIG 1002 MALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>3"FIG 1002 FEMALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>4"FIG 1002 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>4"FIG 1002 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0509</t>
+  </si>
+  <si>
+    <t>0510</t>
+  </si>
+  <si>
+    <t>5"FIG 1002 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>5"FIG 1002 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0517</t>
+  </si>
+  <si>
+    <t>0518</t>
+  </si>
+  <si>
+    <t>4"FIG 1502 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>4"FIG 1502 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>0507</t>
+  </si>
+  <si>
+    <t>0508</t>
+  </si>
+  <si>
+    <t>3"FIG 2202 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>3"FIG 2202 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>01282</t>
+  </si>
+  <si>
+    <t>01283</t>
+  </si>
+  <si>
+    <t>4"FIG 206 FEMALE PLUG(DIE USE MF 0829-01)</t>
+  </si>
+  <si>
+    <t>4"FIG 602 FEMALE PLUG(DIE USE MF 0829-01)</t>
+  </si>
+  <si>
+    <t>0424-01</t>
+  </si>
+  <si>
+    <t>0425-01</t>
+  </si>
+  <si>
+    <t>100 RCS A105</t>
+  </si>
+  <si>
+    <t>21 PCS FORGING OK,PENDING 30</t>
+  </si>
+  <si>
+    <t>21+21 PCS FORGING OK,PENDING 30+30</t>
+  </si>
+  <si>
+    <t>27+54+21 PCS FORGING OK,PENDING 25+20</t>
+  </si>
+  <si>
+    <t>600PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>100pcs(1st shipment)FORGING OK 288</t>
+  </si>
+  <si>
+    <t>22+22 PCS FORGING OK,PENDING 30+30</t>
+  </si>
+  <si>
+    <t>23+23+15 PCS FORGING OK,PENDING 30+30+10</t>
+  </si>
+  <si>
+    <t>530pcs(1st shipment)(FORGING AT MANGALAM TECHNO)1400 FORGING OK</t>
+  </si>
+  <si>
+    <t>860pcs(1st shipment) 860PCS FORGING OK,PENDING 790</t>
+  </si>
+  <si>
+    <t>1305pcs(1st shipment) 1305 FORGING OK,PENDING 570</t>
+  </si>
+  <si>
+    <t>2"FIG 1502 NUT</t>
+  </si>
+  <si>
+    <t>75 RCS</t>
+  </si>
+  <si>
+    <t>1660PCS FORGING OK</t>
+  </si>
+  <si>
+    <t>4"FIG 602 MALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>4"FIG 602 FEMALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>4"FIG 602 MALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>4"FIG 602 FEMALE B/W SCH XXH</t>
+  </si>
+  <si>
+    <t>2"FIG 100 MALE THRD</t>
+  </si>
+  <si>
+    <t>2"FIG 100 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>2"FIG 100 MALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>2"FIG 100 FEMALE B/W SCH 80</t>
+  </si>
+  <si>
+    <t>0186-02</t>
+  </si>
+  <si>
+    <t>0187-02</t>
+  </si>
+  <si>
+    <t>56 DIA A105</t>
+  </si>
+  <si>
+    <t>0495</t>
+  </si>
+  <si>
+    <t>0496</t>
+  </si>
+  <si>
+    <t>1050PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>320PCS FORGING OK</t>
+  </si>
+  <si>
+    <t>400PCS FORGING OK</t>
+  </si>
+  <si>
+    <t>150PCS FORGING OK</t>
+  </si>
+  <si>
+    <t>50PCS FORGING OK</t>
+  </si>
+  <si>
+    <t>200PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>700PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>300PCS FORGING OK(JAY MAHADEV)</t>
+  </si>
+  <si>
+    <t>200PCS FORGING OK(JAY MAHADEV)</t>
+  </si>
+  <si>
+    <t>360pcs(1st shipment)FORGING OK 600PCS</t>
+  </si>
+  <si>
+    <t>750PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>225PCS FORGING OK</t>
+  </si>
+  <si>
+    <t>750PCS FORGINGOK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>SEAT RING(2TONNE HAMMER)</t>
+  </si>
+  <si>
+    <t>3+2PCS SAMPLING 200 RCS A105/200 RCS 4130 CUT WT 140 TO 146KGS</t>
+  </si>
+  <si>
+    <t>N60 CHOKE HAND WHEEL 9"</t>
+  </si>
+  <si>
+    <t>01166</t>
+  </si>
+  <si>
+    <t>DI CASTING</t>
+  </si>
+  <si>
+    <t>ORDER AT PLASMA</t>
+  </si>
+  <si>
+    <t>5"HU FIG 1002 MALE SUB</t>
+  </si>
+  <si>
+    <t>5"HU FIG 1002 FEMALE SUB</t>
+  </si>
+  <si>
+    <t>01213</t>
+  </si>
+  <si>
+    <t>01214</t>
+  </si>
+  <si>
+    <t>MERAK</t>
+  </si>
+  <si>
+    <t>MHPL014/22.05.26</t>
+  </si>
+  <si>
+    <t>60pcs(1st shipment)FORGING OK 100PCS</t>
+  </si>
+  <si>
+    <t>FORGING OK 70PCS</t>
+  </si>
+  <si>
+    <t>FORGING OK 200PCS</t>
+  </si>
+  <si>
+    <t>CUTTING READY FOR FOTGING 200PCS</t>
+  </si>
+  <si>
+    <t>CUTTING READY FOR FORGING 200PCS</t>
+  </si>
+  <si>
+    <t>FORGING OK 50PCS</t>
+  </si>
+  <si>
+    <t>FORGING OK 60PCS</t>
+  </si>
+  <si>
+    <t>DIE USE MF 0827,FORGING OK 50PCS</t>
+  </si>
+  <si>
+    <t>DIE USE MF 0829,FORGING OK 50PCS</t>
+  </si>
+  <si>
+    <t>use forging drg# 0829-01,FORGING OK 50PCS</t>
+  </si>
+  <si>
+    <t>DIE USE MF 0829,FORGING OK 25PCS</t>
+  </si>
+  <si>
+    <t>use forging drg# 0829-01,FORGING OK 25PCS</t>
+  </si>
+  <si>
+    <t>FORGING OK 20PCS</t>
+  </si>
+  <si>
+    <t>1050PCS'FORGING OK(FORGING AT MANGALAM TECHNO)</t>
+  </si>
+  <si>
+    <t>CUTTING OK 100PCS</t>
+  </si>
+  <si>
+    <t>50PCS 'P/MC IN STOCK MF 0828</t>
+  </si>
+  <si>
+    <t>60 PCS'P/MC IN STOCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CUTTING OK 100PCS</t>
+  </si>
+  <si>
+    <t>CUTTING OK 25PCS</t>
+  </si>
+  <si>
+    <t>CUTTING OK 50PCS</t>
+  </si>
+  <si>
+    <t>CUTTING OK 40PCS</t>
+  </si>
+  <si>
+    <t>CUTTING OK 20PCS</t>
+  </si>
+  <si>
+    <t>680pcs(1st shipment)FORGING OK 883PCS</t>
+  </si>
+  <si>
+    <t>12PCS FORGING OK,PENDING 38PCS</t>
+  </si>
+  <si>
+    <t>22PCS FORGING OK,PENDING 28PCS</t>
+  </si>
+  <si>
+    <t>34+22PCS FORGING OK,PENDING 16+28PCS</t>
+  </si>
+  <si>
+    <t>FORGING OK 100PCS</t>
+  </si>
+  <si>
+    <t>01291</t>
+  </si>
+  <si>
+    <t>2 1/2"FIG 100 MALE THRD</t>
+  </si>
+  <si>
+    <t>2 1/2"FIG 100 FEMALE THRD</t>
+  </si>
+  <si>
+    <t>30pcs(1st shipment)</t>
+  </si>
+  <si>
+    <t>01292</t>
+  </si>
+  <si>
+    <t>01293</t>
+  </si>
+  <si>
+    <t>FORGING OK 250PCS</t>
+  </si>
+  <si>
+    <t>FOEGING OK 100PCS</t>
+  </si>
+  <si>
+    <t>UNDER CUTTING</t>
+  </si>
+  <si>
+    <t>30pcs(1st shipment)FORGING OK 100PCS</t>
+  </si>
+  <si>
+    <t>2"FIIG 2202 SPLIT BUSH</t>
+  </si>
+  <si>
+    <t>2.25/43MM</t>
+  </si>
+  <si>
+    <t>4"FIG 206 MALE HOSE</t>
+  </si>
+  <si>
+    <t>4"FIG 206 FEMALE HOSE</t>
+  </si>
+  <si>
+    <t>01294</t>
+  </si>
+  <si>
+    <t>01295</t>
+  </si>
+  <si>
+    <t>PF262700056/   05.06.26</t>
+  </si>
+  <si>
+    <t>12 X 150 WN SCH 40 WITH 4 X 150 SORF</t>
+  </si>
+  <si>
+    <t>16/8/3 X 150 SORF</t>
+  </si>
+  <si>
+    <t>PARAMOUNT</t>
+  </si>
+  <si>
+    <t>200 RCS A105</t>
+  </si>
+  <si>
+    <t>PF262700060/   09.06.26</t>
+  </si>
+  <si>
+    <t>3 X 300 SORF</t>
+  </si>
+  <si>
+    <t>3 X 300 SOFF</t>
+  </si>
+  <si>
+    <t>4 X 300 SORF</t>
+  </si>
+  <si>
+    <t>4 X 300 SOFF</t>
+  </si>
+  <si>
+    <t>6 X 300 SORF WITH 2 X 150 SORF</t>
+  </si>
+  <si>
+    <t>6 X 300 SOFF WITH 2 X 150 SORF</t>
+  </si>
+  <si>
+    <t>4 X 300 WNRF SCH 40</t>
+  </si>
+  <si>
+    <t>63 DIA 1018</t>
+  </si>
+  <si>
+    <t>72 DIA 1018</t>
+  </si>
+  <si>
+    <t>2"1502 PLUG VALVE NUT</t>
+  </si>
+  <si>
+    <t>01314</t>
+  </si>
+  <si>
+    <t>TEPL06-26/16.06.26</t>
+  </si>
+  <si>
+    <t>BON HUB</t>
+  </si>
+  <si>
+    <t>0681</t>
+  </si>
+  <si>
+    <t>TATVAMASI</t>
+  </si>
+  <si>
+    <t>160 DIA36CRMN5</t>
+  </si>
+  <si>
+    <t>1.1/'44MM</t>
+  </si>
+  <si>
+    <t>1.4/'44MM</t>
+  </si>
+  <si>
+    <t>1.4/44MM</t>
+  </si>
+  <si>
+    <t>20pcs(1st shipment)DIRECT CUTTING OK 200PCS</t>
+  </si>
+  <si>
+    <t>20pcs(1st shipment)DIRECT CUTTING  OK 50PCS</t>
+  </si>
+  <si>
+    <t>PCFI-160007/28.05.26</t>
+  </si>
+  <si>
+    <t>DECKEL DN150 AVR</t>
+  </si>
+  <si>
+    <t>DECKEL DN125 AVR</t>
+  </si>
+  <si>
+    <t>DECKEL DN200 AVR</t>
+  </si>
+  <si>
+    <t>01308</t>
+  </si>
+  <si>
+    <t>01307</t>
+  </si>
+  <si>
+    <t>01309</t>
+  </si>
+  <si>
+    <t>PRINS CAST</t>
+  </si>
+  <si>
+    <t>RSFGH2600243/          18.06.26</t>
+  </si>
+  <si>
+    <t>13"SLIP BOWL</t>
+  </si>
+  <si>
+    <t>0334</t>
+  </si>
+  <si>
+    <t>GBI</t>
+  </si>
+  <si>
+    <t>RSFGH2600244/          19.06.26</t>
+  </si>
+  <si>
+    <t>BLANKING PLUG 10K JWA</t>
+  </si>
+  <si>
+    <t>01171</t>
+  </si>
+  <si>
+    <t>5.9/94MM</t>
+  </si>
+  <si>
+    <t>FORGING OK 450PCS</t>
+  </si>
+  <si>
+    <t>50pcs(1st shipment)FORGING OK 75PCS</t>
+  </si>
+  <si>
+    <t>25PCS FORGING OK,PENDING 25PCS</t>
+  </si>
+  <si>
+    <t>50pcs(1st shipment)FORGING OK 200PCS</t>
+  </si>
+  <si>
+    <t>0443-01</t>
+  </si>
+  <si>
+    <t>RSFGH2600240/          23.06.26</t>
+  </si>
+  <si>
+    <t>2 9/16 5M X 2&amp;3LP COMP</t>
+  </si>
+  <si>
+    <t>0604</t>
   </si>
   <si>
     <t>125 DIA 4130</t>
   </si>
   <si>
-    <t>new cut wt 35.75</t>
+    <t>2 9/16 5M X 3"SCH XXH WN</t>
+  </si>
+  <si>
+    <t>0199</t>
+  </si>
+  <si>
+    <t>1 13/16 15M X 2LP COMP</t>
+  </si>
+  <si>
+    <t>0466-02</t>
+  </si>
+  <si>
+    <t>RSFGH2600257/          25.06.26</t>
+  </si>
+  <si>
+    <t>1 13/16 10M X 2"SCH XXH/80 WN</t>
+  </si>
+  <si>
+    <t>0327</t>
+  </si>
+  <si>
+    <t>1 13/16 15M X 2"SCH XXH WN</t>
+  </si>
+  <si>
+    <t>0462-02</t>
+  </si>
+  <si>
+    <t>RSFGH2600259/          25.06.26</t>
+  </si>
+  <si>
+    <t>2 1/16 5M X 3"SCH XXH/80 WN</t>
+  </si>
+  <si>
+    <t>2 1/16 5M X 2"SCH XXH/80 WN</t>
+  </si>
+  <si>
+    <t>0197-06</t>
+  </si>
+  <si>
+    <t>0197</t>
+  </si>
+  <si>
+    <t>RSFGH2600261/          25.06.26</t>
+  </si>
+  <si>
+    <t>2 1/16 10M X 2"SCH 80/XXH WN</t>
+  </si>
+  <si>
+    <t>0295</t>
+  </si>
+  <si>
+    <t>2 1/16 10M X 3"SCH XXH WN</t>
+  </si>
+  <si>
+    <t>0295-01</t>
+  </si>
+  <si>
+    <t>110/125 DIA 4130</t>
+  </si>
+  <si>
+    <t>2 9/16 5M X 3"&amp;2"SCH 80 WN</t>
+  </si>
+  <si>
+    <t>2 9/16 5M X 4"SCH 80 WN</t>
+  </si>
+  <si>
+    <t>0199-01</t>
+  </si>
+  <si>
+    <t>RSFGH2600252/          25.06.26</t>
+  </si>
+  <si>
+    <t>RSFGH2600262/          25.06.26</t>
+  </si>
+  <si>
+    <t>RSFGH2600263/          25.06.26</t>
+  </si>
+  <si>
+    <t>3 1/16 10M X 3"SCH 80/XXH WN</t>
+  </si>
+  <si>
+    <t>0253</t>
+  </si>
+  <si>
+    <t>3+3PCS SAMPLING MS&amp;SS410 CUT WT 3.2/3.3KGS</t>
   </si>
   <si>
     <t>MATERIAL READY FOR CUTTING</t>
   </si>
   <si>
-    <t>112P</t>
-  </si>
-  <si>
-    <t>ELITE H2 BONNET 5K</t>
-  </si>
-  <si>
-    <t>01236</t>
-  </si>
-  <si>
-    <t>28/313MM</t>
-  </si>
-  <si>
-    <t>120 DIA 4130</t>
-  </si>
-  <si>
-    <t>ELITE H2 WING NUT(1511)</t>
-  </si>
-  <si>
-    <t>01241</t>
-  </si>
-  <si>
-    <t>ECS-780/03.02.26</t>
-  </si>
-  <si>
-    <t>110 DIA 4130</t>
-  </si>
-  <si>
-    <t>WAIT FOR MAERIAL</t>
-  </si>
-  <si>
-    <t>ECS-786/04.02.26</t>
+    <t>0477/81</t>
+  </si>
+  <si>
+    <t>0477-01/81</t>
+  </si>
+  <si>
+    <t>0336</t>
+  </si>
+  <si>
+    <t>200 DIA 4130</t>
+  </si>
+  <si>
+    <t>RSFGH2600267/          27.06.26</t>
+  </si>
+  <si>
+    <t>RSFGH2600271/          27.06.26</t>
+  </si>
+  <si>
+    <t>JWA 10K BONNET</t>
+  </si>
+  <si>
+    <t>01172</t>
+  </si>
+  <si>
+    <t>12.65/201MM</t>
+  </si>
+  <si>
+    <t>2 1/16 10M CHOKE BODY(0451)</t>
+  </si>
+  <si>
+    <t>01175</t>
+  </si>
+  <si>
+    <t>RSFGH2600270/          27.06.26</t>
+  </si>
+  <si>
+    <t>TEE BODY N60 WITH CAGE NIPPLE</t>
+  </si>
+  <si>
+    <t>01185</t>
+  </si>
+  <si>
+    <t>100/110 DIA 4130</t>
+  </si>
+  <si>
+    <t>2"WING NUT N60</t>
+  </si>
+  <si>
+    <t>01176</t>
+  </si>
+  <si>
+    <t>01173</t>
+  </si>
+  <si>
+    <t>BONNET N60</t>
+  </si>
+  <si>
+    <t>8.9/222MM</t>
+  </si>
+  <si>
+    <t>01225</t>
+  </si>
+  <si>
+    <t>CHOKE WING NUT 15K JWA FOR ASSEMBLY</t>
+  </si>
+  <si>
+    <t>2 1/16 10 JWA NUT FOR ASSEMBLY</t>
+  </si>
+  <si>
+    <t>RSFGH2600270/         27.06.26</t>
+  </si>
+  <si>
+    <t>90/100 DIA 4130</t>
+  </si>
+  <si>
+    <t>01315</t>
+  </si>
+  <si>
+    <t>UNDER FORGING AT MANGALAM</t>
+  </si>
+  <si>
+    <t>RDI-386935/25.06.26</t>
+  </si>
+  <si>
+    <t>PUP JOINT BODY 3"1502 MXF 3FT</t>
+  </si>
+  <si>
+    <t>PUP JOINT BODY 3"1502 MXF 2FT</t>
+  </si>
+  <si>
+    <t>01320</t>
+  </si>
+  <si>
+    <t>01317</t>
+  </si>
+  <si>
+    <t>RDI</t>
+  </si>
+  <si>
+    <t>616MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSFGH2600276/77           02.07.26          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSFGH2600277/           03.07.26          </t>
   </si>
   <si>
     <t>2 1/16 15M CHOKE BODY</t>
@@ -311,1088 +1667,26 @@
     <t>01226</t>
   </si>
   <si>
-    <t>200 RCS 4130</t>
-  </si>
-  <si>
-    <t>ORDER QTY 375PCS,(SCHEDULE 125PCS EVERY 3MONTH) FORGING DONE 263PCS,BALANCE 112PCS PENDING,WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>SEALAND</t>
-  </si>
-  <si>
-    <t>SCC-P18029/20.02.26</t>
-  </si>
-  <si>
-    <t>8"FIG 100/200/206 NUT WITH 3 X 150 SORF</t>
-  </si>
-  <si>
-    <t>0494/0083</t>
-  </si>
-  <si>
-    <t>160 RCS A105</t>
-  </si>
-  <si>
-    <t>6"FIG 100/200/206 NUT</t>
-  </si>
-  <si>
-    <t>0120</t>
-  </si>
-  <si>
-    <t>125 RCS A105</t>
-  </si>
-  <si>
-    <t>5"FIG 100/200/206 NUT</t>
-  </si>
-  <si>
-    <t>01100</t>
-  </si>
-  <si>
-    <t>130 RCS A105</t>
-  </si>
-  <si>
-    <t>100 DIA 4130</t>
-  </si>
-  <si>
-    <t>180 DIA 4130</t>
-  </si>
-  <si>
-    <t>PARAMOUNT</t>
-  </si>
-  <si>
-    <t>CUTTING READY FOR FORGING</t>
-  </si>
-  <si>
-    <t>190 DIA 4130</t>
-  </si>
-  <si>
-    <t>0862</t>
-  </si>
-  <si>
-    <t>125 RCS 4130</t>
-  </si>
-  <si>
-    <t>INTEGRAL TEE 2"1502</t>
-  </si>
-  <si>
-    <t>4"FIG 100/200/206 NUT</t>
-  </si>
-  <si>
-    <t>0423</t>
-  </si>
-  <si>
-    <t>4"FIG 602/1002 NUT</t>
-  </si>
-  <si>
-    <t>5"FIG 1002 NUT</t>
-  </si>
-  <si>
-    <t>3"FIG 1502 NUT</t>
-  </si>
-  <si>
-    <t>4"FIG 1502 NUT</t>
-  </si>
-  <si>
-    <t>0511</t>
-  </si>
-  <si>
-    <t>0516</t>
-  </si>
-  <si>
-    <t>0498</t>
-  </si>
-  <si>
-    <t>0506</t>
-  </si>
-  <si>
-    <t>3"FIG 1502 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>3"FIG 1502 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0499</t>
-  </si>
-  <si>
-    <t>0500</t>
-  </si>
-  <si>
-    <t>80 DIA 4130</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0446</t>
-  </si>
-  <si>
-    <t>0447</t>
-  </si>
-  <si>
-    <t>1"FIG 200/206 NUT</t>
-  </si>
-  <si>
-    <t>1 1/4"FIG 200 NUT</t>
-  </si>
-  <si>
-    <t>1 1/2" FIG 200 NUT</t>
-  </si>
-  <si>
-    <t>2"FIG 100/200/206 NUT</t>
-  </si>
-  <si>
-    <t>2 1/2"FIG 100 NUT</t>
-  </si>
-  <si>
-    <t>3"FIG 100/200/206 NUT</t>
-  </si>
-  <si>
-    <t>0121</t>
-  </si>
-  <si>
-    <t>0119</t>
-  </si>
-  <si>
-    <t>0428</t>
-  </si>
-  <si>
-    <t>250pcs(1st shipment) WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>20pcs(1st shipment) WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>40pcs(1st shipment) WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>30pcs(1st shipment) WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>4"FIG 207 NUT</t>
-  </si>
-  <si>
-    <t>01271</t>
-  </si>
-  <si>
-    <t>1"FIG 602/1002 NUT</t>
-  </si>
-  <si>
-    <t>1 1/2"FIG 602 NUT</t>
-  </si>
-  <si>
-    <t>2"FIG 602 NUT</t>
-  </si>
-  <si>
-    <t>3"FIG 602/1002 NUT</t>
-  </si>
-  <si>
-    <t>0491</t>
-  </si>
-  <si>
-    <t>01093</t>
-  </si>
-  <si>
-    <t>0441</t>
-  </si>
-  <si>
-    <t>0488</t>
-  </si>
-  <si>
-    <t>370pcs(1st shipment) WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>200pcs(1st shipment) WAIT FOR MATERIAL</t>
-  </si>
-  <si>
-    <t>2"FIG 2202 NUT</t>
-  </si>
-  <si>
-    <t>01064</t>
-  </si>
-  <si>
-    <t>3"FIG 2202 NUT</t>
-  </si>
-  <si>
-    <t>0492</t>
-  </si>
-  <si>
-    <t>0493</t>
-  </si>
-  <si>
-    <t>SELAND</t>
-  </si>
-  <si>
-    <t>70 DIA 4130</t>
-  </si>
-  <si>
-    <t>1.6/51MM</t>
-  </si>
-  <si>
-    <t>1.8/58MM</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 MALE PLUG</t>
-  </si>
-  <si>
-    <t>0774</t>
-  </si>
-  <si>
-    <t>50+50</t>
-  </si>
-  <si>
-    <t>6.5/106MM</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 FEMALE PLUG</t>
-  </si>
-  <si>
-    <t>0775</t>
-  </si>
-  <si>
-    <t>3"FIG 1502 MALE PLUG</t>
-  </si>
-  <si>
-    <t>0827</t>
-  </si>
-  <si>
-    <t>30+30</t>
-  </si>
-  <si>
-    <t>01296</t>
-  </si>
-  <si>
-    <t>25+25</t>
-  </si>
-  <si>
-    <t>3"FIG 602 MALE PLUG(DIE USE MF 0827)</t>
-  </si>
-  <si>
-    <t>4"FIG 602 MALE PLUG(DIE USE MF 0829)</t>
-  </si>
-  <si>
-    <t>01298</t>
-  </si>
-  <si>
-    <t>4"FIG 206 MALE PLUG(DIE USE MF 0829)</t>
-  </si>
-  <si>
-    <t>01302</t>
-  </si>
-  <si>
-    <t>3"FIG 1502 FEMALE PLUG</t>
-  </si>
-  <si>
-    <t>0828</t>
-  </si>
-  <si>
-    <t>3"FIG 602 FEMALE PLUG(P/MC STOCK 0828)</t>
-  </si>
-  <si>
-    <t>140 DIA 4130</t>
-  </si>
-  <si>
-    <t>P/MC IN STOCK MF 0828</t>
-  </si>
-  <si>
-    <t>P/MC IN STOCK</t>
-  </si>
-  <si>
-    <t>01299</t>
-  </si>
-  <si>
-    <t>01303</t>
-  </si>
-  <si>
-    <t>30 M/C IN STOCK(SOUR)BALANCE CUTTING OK</t>
-  </si>
-  <si>
-    <t>5"FIG 1002 MALE PLUG</t>
-  </si>
-  <si>
-    <t>5"FIG 1002 FEMALE PLUG</t>
-  </si>
-  <si>
-    <t>01300</t>
-  </si>
-  <si>
-    <t>01301</t>
-  </si>
-  <si>
-    <t>22.15/97MM</t>
-  </si>
-  <si>
-    <t>1 1/2"FIG 602 MALE THREAD</t>
-  </si>
-  <si>
-    <t>1"FIG 602 FEMALE THREAD</t>
-  </si>
-  <si>
-    <t>1"FIG 602 MALE THREAD</t>
-  </si>
-  <si>
-    <t>1 1/2"FIG 602 FEMALE THREAD</t>
-  </si>
-  <si>
-    <t>0486</t>
-  </si>
-  <si>
-    <t>0487</t>
-  </si>
-  <si>
-    <t>0489</t>
-  </si>
-  <si>
-    <t>0490</t>
-  </si>
-  <si>
-    <t>4"FIG 602 MALE THREAD</t>
-  </si>
-  <si>
-    <t>4"FIG 602 FEMALE THREAD</t>
-  </si>
-  <si>
-    <t>01096</t>
-  </si>
-  <si>
-    <t>01097</t>
-  </si>
-  <si>
-    <t>1"FIG 1002 MALE THREAD</t>
-  </si>
-  <si>
-    <t>1"FIG 1002 FEMALE THREAD</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 MALE THREAD</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 FEMALE THREAD</t>
-  </si>
-  <si>
-    <t>0448</t>
-  </si>
-  <si>
-    <t>0449</t>
-  </si>
-  <si>
-    <t>50pcs(1st shipment)</t>
-  </si>
-  <si>
-    <t>30pcs(1st shipment)</t>
-  </si>
-  <si>
-    <t>20pcs(1st shipment)</t>
-  </si>
-  <si>
-    <t>200pcs(1st shipment)MATERIAL READY FOR CUTTING</t>
-  </si>
-  <si>
-    <t>20.4/98MM</t>
-  </si>
-  <si>
-    <t>FORGING OK</t>
-  </si>
-  <si>
-    <t>DIE USE MF 0827,FORGING OK</t>
-  </si>
-  <si>
-    <t>CUTTING OK</t>
-  </si>
-  <si>
-    <t>RSFGH2600088/                 05.03.26</t>
-  </si>
-  <si>
-    <t>2 9/16 10M X 2"1502 MALE WECO</t>
-  </si>
-  <si>
-    <t>0748</t>
-  </si>
-  <si>
-    <t>2 9/16 15M X 2"1502 FEMALE WECO</t>
-  </si>
-  <si>
-    <t>01008</t>
-  </si>
-  <si>
-    <t>7.2/96MM</t>
-  </si>
-  <si>
-    <t>CROSSOVER 2"1502 MALE X MALE</t>
-  </si>
-  <si>
-    <t>CROSSOVER 2"1502 MALE X FEMALE</t>
-  </si>
-  <si>
-    <t>0923</t>
-  </si>
-  <si>
-    <t>0931</t>
-  </si>
-  <si>
-    <t>25+15</t>
-  </si>
-  <si>
-    <t>8.0/160MM</t>
-  </si>
-  <si>
-    <t>12.0/160MM</t>
-  </si>
-  <si>
-    <t>CROSSOVER 2"1502 MALE X 3"1502 FEMALE</t>
-  </si>
-  <si>
-    <t>CROSSOVER 3"1502 MALE X 2"1502 FEMALE</t>
-  </si>
-  <si>
-    <t>0801</t>
-  </si>
-  <si>
-    <t>0800</t>
-  </si>
-  <si>
-    <t>CROSSOVER 2"1502 FEMALE X FEMALE</t>
-  </si>
-  <si>
-    <t>CROSSOVER 3"1502 MALE X MALE</t>
-  </si>
-  <si>
-    <t>0922</t>
-  </si>
-  <si>
-    <t>0967</t>
-  </si>
-  <si>
-    <t>DIE USE MF 0829,FORGING OK</t>
-  </si>
-  <si>
-    <t>16.5/185MM</t>
-  </si>
-  <si>
-    <t>RSFGH2600107            12.03.26</t>
-  </si>
-  <si>
-    <t>NOV</t>
-  </si>
-  <si>
-    <t>3"5M SQURE FLANGE 4-BOLT SCH XXH</t>
-  </si>
-  <si>
-    <t>0273</t>
-  </si>
-  <si>
-    <t>120/125 RCS 4130</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 'PLUG VALVE BODY</t>
-  </si>
-  <si>
-    <t>01304</t>
-  </si>
-  <si>
-    <t>RSFGH2600108/                 014.03.26</t>
-  </si>
-  <si>
-    <t>PLUG FEMALE 3"1502 SOLID&amp;9/16"</t>
-  </si>
-  <si>
-    <t>12.6/104MM</t>
-  </si>
-  <si>
-    <t>80/90 DIA 4130</t>
-  </si>
-  <si>
-    <t>65 RCS A105</t>
-  </si>
-  <si>
-    <t>77 RCS A105</t>
-  </si>
-  <si>
-    <t>2"FIG 2202 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>2"FIG 2202 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>01280</t>
-  </si>
-  <si>
-    <t>01281</t>
-  </si>
-  <si>
-    <t>4.25/106MM</t>
-  </si>
-  <si>
-    <t>6.0/1069MM</t>
-  </si>
-  <si>
-    <t>95 DIA 4130</t>
-  </si>
-  <si>
-    <t>3"FIG 100/200/206 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0502</t>
-  </si>
-  <si>
-    <t>0503</t>
-  </si>
-  <si>
-    <t>3"FIG 100/200/206 MALE THRD</t>
-  </si>
-  <si>
-    <t>3"FIG 100/200/206 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>3"FIG 100/200/206 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>0429</t>
-  </si>
-  <si>
-    <t>0430</t>
-  </si>
-  <si>
-    <t>95pcs(1st shipment)FORGING OK,PENDING 130</t>
-  </si>
-  <si>
-    <t>155pcs(1st shipment)FORGING OK,PENDING 145</t>
-  </si>
-  <si>
-    <t>80pcs(1st shipment)FORGING OK,PENDING 120</t>
-  </si>
-  <si>
-    <t>40pcs FORGING OK,PENDING 210</t>
-  </si>
-  <si>
-    <t>4"FIG 100 MALE THRD</t>
-  </si>
-  <si>
-    <t>4"FIG 100 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>0426</t>
-  </si>
-  <si>
-    <t>0427</t>
-  </si>
-  <si>
-    <t>4"FIG 200/206 MALE B/W</t>
-  </si>
-  <si>
-    <t>4"FIG 200/206 FEMALE B/W</t>
-  </si>
-  <si>
-    <t>4"FIG 200/206 MALE THRD</t>
-  </si>
-  <si>
-    <t>4"FIG 200/206 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>0504</t>
-  </si>
-  <si>
-    <t>0505</t>
-  </si>
-  <si>
-    <t>0514</t>
-  </si>
-  <si>
-    <t>0515</t>
-  </si>
-  <si>
-    <t>5"FIG 100 MALE B/W</t>
-  </si>
-  <si>
-    <t>5"FIG 100 FEMALE B/W</t>
-  </si>
-  <si>
-    <t>5"FIG 100 MALE THRD</t>
-  </si>
-  <si>
-    <t>5"FIG 100 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>5"FIG 200/206 MALE THRD</t>
-  </si>
-  <si>
-    <t>5"FIG 200/206 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>6"FIG 100 MALE B/W</t>
-  </si>
-  <si>
-    <t>6"FIG 100 FEMALE B/W</t>
-  </si>
-  <si>
-    <t>6"FIG 200/206 MALE B/W</t>
-  </si>
-  <si>
-    <t>6"FIG 200/206 FEMALE B/W</t>
-  </si>
-  <si>
-    <t>6"FIG 100/200/206 MALE THRD</t>
-  </si>
-  <si>
-    <t>6"FIG 100/200/206 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>50+50+50</t>
-  </si>
-  <si>
-    <t>8"FIG 100/200 MALE B/W</t>
-  </si>
-  <si>
-    <t>8"FIG 100/200 FEMALE B/W</t>
-  </si>
-  <si>
-    <t>8"FIG 100/200/206 MALE THRD</t>
-  </si>
-  <si>
-    <t>8"FIG 100/200/206 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>50+50+25</t>
-  </si>
-  <si>
-    <t>16 X 150 WNRF SCH 40</t>
-  </si>
-  <si>
-    <t>01083</t>
-  </si>
-  <si>
-    <t>BHEL-25328/17.02.26</t>
-  </si>
-  <si>
-    <t>2 9/16"5000PSI BONNET FGV</t>
-  </si>
-  <si>
-    <t>3 1/8"-3000/5000PSI GATE</t>
-  </si>
-  <si>
-    <t>2 1/16"10000PSI VALVE BODY FBV</t>
-  </si>
-  <si>
-    <t>01274</t>
-  </si>
-  <si>
-    <t>01276</t>
-  </si>
-  <si>
-    <t>01275</t>
-  </si>
-  <si>
-    <t>01277</t>
-  </si>
-  <si>
-    <t>01273</t>
-  </si>
-  <si>
-    <t>BHEL</t>
-  </si>
-  <si>
-    <t>SS410</t>
-  </si>
-  <si>
-    <t>125 RCS'A105</t>
-  </si>
-  <si>
-    <t>01094-01</t>
-  </si>
-  <si>
-    <t>01095-01</t>
-  </si>
-  <si>
-    <t>01098-01</t>
-  </si>
-  <si>
-    <t>01099-01</t>
-  </si>
-  <si>
-    <t>1 1/4"FIG 200 MALE THRD</t>
-  </si>
-  <si>
-    <t>1 1/4"FIG 200 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>01286</t>
-  </si>
-  <si>
-    <t>01287</t>
-  </si>
-  <si>
-    <t>1 1/2" FIG 200 MALE THRD</t>
-  </si>
-  <si>
-    <t>01289</t>
-  </si>
-  <si>
-    <t>01290</t>
-  </si>
-  <si>
-    <t>1 1/2" FIG 200 MALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>1 1/2" FIG 200 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>1 1/2" FIG 200 FEMALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>1 1/2"FIG 602 MALE B/W SCH 160</t>
-  </si>
-  <si>
-    <t>1 1/2"FIG 602 FEMALE B/W SCH 160</t>
-  </si>
-  <si>
-    <t>01094</t>
-  </si>
-  <si>
-    <t>01095</t>
-  </si>
-  <si>
-    <t>2"FIG 602 MALE THRD</t>
-  </si>
-  <si>
-    <t>2"FIG 602 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>2"FIG 602 MALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>2"FIG 602 FEMALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>0442</t>
-  </si>
-  <si>
-    <t>0443</t>
-  </si>
-  <si>
-    <t>100pcs(1st shipment)</t>
-  </si>
-  <si>
-    <t>3"FIG 602 MALE THRD</t>
-  </si>
-  <si>
-    <t>3"FIG 602 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>3"FIG 602 MALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>3"FIG 602 FEMALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>3"FIG 602 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>3"FIG 602 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0512</t>
-  </si>
-  <si>
-    <t>0513</t>
-  </si>
-  <si>
-    <t>3"FIG 1002 MALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>3"FIG 1002 FEMALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>4"FIG 1002 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>4"FIG 1002 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0509</t>
-  </si>
-  <si>
-    <t>0510</t>
-  </si>
-  <si>
-    <t>5"FIG 1002 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>5"FIG 1002 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0517</t>
-  </si>
-  <si>
-    <t>0518</t>
-  </si>
-  <si>
-    <t>4"FIG 1502 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>4"FIG 1502 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>0507</t>
-  </si>
-  <si>
-    <t>0508</t>
-  </si>
-  <si>
-    <t>3"FIG 2202 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>3"FIG 2202 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>01282</t>
-  </si>
-  <si>
-    <t>01283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNDER FORGING </t>
-  </si>
-  <si>
-    <t>4"FIG 206 FEMALE PLUG(DIE USE MF 0829-01)</t>
-  </si>
-  <si>
-    <t>4"FIG 602 FEMALE PLUG(DIE USE MF 0829-01)</t>
-  </si>
-  <si>
-    <t>use forging drg# 0829-01,FORGING OK</t>
-  </si>
-  <si>
-    <t>85/95 SS410 DIA MATERIAL IN STOCK</t>
-  </si>
-  <si>
-    <t>0424-01</t>
-  </si>
-  <si>
-    <t>0425-01</t>
-  </si>
-  <si>
-    <t>100 RCS A105</t>
-  </si>
-  <si>
-    <t>22PCS CUTTING READY FOR FORGING</t>
-  </si>
-  <si>
-    <t>12PCS CUTTING READY FOR FORGING</t>
-  </si>
-  <si>
-    <t>34+22PCS CUTTING READY FOR FORGING</t>
-  </si>
-  <si>
-    <t>680pcs(1st shipment)UNDER FORGING 883</t>
-  </si>
-  <si>
-    <t>FORGING OK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>21 PCS FORGING OK,PENDING 30</t>
-  </si>
-  <si>
-    <t>21+21 PCS FORGING OK,PENDING 30+30</t>
-  </si>
-  <si>
-    <t>27+54+21 PCS FORGING OK,PENDING 25+20</t>
-  </si>
-  <si>
-    <t>600PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>100pcs(1st shipment)FORGING OK 288</t>
-  </si>
-  <si>
-    <t>22+22 PCS FORGING OK,PENDING 30+30</t>
-  </si>
-  <si>
-    <t>23+23+15 PCS FORGING OK,PENDING 30+30+10</t>
-  </si>
-  <si>
-    <t>530pcs(1st shipment)(FORGING AT MANGALAM TECHNO)1400 FORGING OK</t>
-  </si>
-  <si>
-    <t>860pcs(1st shipment) 860PCS FORGING OK,PENDING 790</t>
-  </si>
-  <si>
-    <t>1305pcs(1st shipment) 1305 FORGING OK,PENDING 570</t>
-  </si>
-  <si>
-    <t>RSFGH2600144            16.04.26</t>
-  </si>
-  <si>
-    <t>3"1502 WING NUT HALF 15000PSI 2-5/8"CT</t>
-  </si>
-  <si>
-    <t>01306</t>
-  </si>
-  <si>
-    <t>PF252600360/                 17.03.26</t>
-  </si>
-  <si>
-    <t>RSFGH2600123/                 17.04.26</t>
-  </si>
-  <si>
-    <t>2 9/16 10M INSTRUMENT FLANGE</t>
-  </si>
-  <si>
-    <t>01257</t>
-  </si>
-  <si>
-    <t>RSFGH2600132/                 17.04.26</t>
-  </si>
-  <si>
-    <t>2"FIG 1502 NUT</t>
-  </si>
-  <si>
-    <t>75 RCS</t>
-  </si>
-  <si>
-    <t>1660PCS FORGING OK</t>
-  </si>
-  <si>
-    <t>4"FIG 602 MALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>4"FIG 602 FEMALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>4"FIG 602 MALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>4"FIG 602 FEMALE B/W SCH XXH</t>
-  </si>
-  <si>
-    <t>2"FIG 100 MALE THRD</t>
-  </si>
-  <si>
-    <t>2"FIG 100 FEMALE THRD</t>
-  </si>
-  <si>
-    <t>2"FIG 100 MALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>2"FIG 100 FEMALE B/W SCH 80</t>
-  </si>
-  <si>
-    <t>0186-02</t>
-  </si>
-  <si>
-    <t>0187-02</t>
-  </si>
-  <si>
-    <t>56 DIA A105</t>
-  </si>
-  <si>
-    <t>0495</t>
-  </si>
-  <si>
-    <t>0496</t>
-  </si>
-  <si>
-    <t>1050PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>320PCS FORGING OK</t>
-  </si>
-  <si>
-    <t>400PCS FORGING OK</t>
-  </si>
-  <si>
-    <t>150PCS FORGING OK</t>
-  </si>
-  <si>
-    <t>50PCS FORGING OK</t>
-  </si>
-  <si>
-    <t>CUTTING READY FOR FOTGING</t>
-  </si>
-  <si>
-    <t>200PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>700PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>300PCS FORGING OK(JAY MAHADEV)</t>
-  </si>
-  <si>
-    <t>200PCS FORGING OK(JAY MAHADEV)</t>
-  </si>
-  <si>
-    <t>360pcs(1st shipment)FORGING OK 600PCS</t>
-  </si>
-  <si>
-    <t>750PCS FORGING OK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>50pcs(1st shipment)UNDER CUTTING 200PCS</t>
-  </si>
-  <si>
-    <t>50pcs(1st shipment)UNDER CUTTING 75PCS</t>
-  </si>
-  <si>
-    <t>225PCS FORGING OK</t>
-  </si>
-  <si>
-    <t>60pcs(1st shipment)UNDER FORGING100PCS</t>
-  </si>
-  <si>
-    <t>RSFGH2600134/               30.04.26</t>
-  </si>
-  <si>
-    <t>2 1/16 5M X 2"SCH XXH&amp;80 WN</t>
-  </si>
-  <si>
-    <t>2 1/16 10M X 2"SCH XXH &amp;80 WN</t>
-  </si>
-  <si>
-    <t>1 13/16 15M X 3"SCH XXH WN</t>
-  </si>
-  <si>
-    <t>0197</t>
-  </si>
-  <si>
-    <t>0295</t>
-  </si>
-  <si>
-    <t>0462-03</t>
-  </si>
-  <si>
-    <t>750PCS FORGINGOK(FORGING AT MANGALAM TECHNO)</t>
-  </si>
-  <si>
-    <t>UNDER CUTTING</t>
-  </si>
-  <si>
-    <t>3PCS SAMPLING 140 DIA 4130 CUT WT 22.300 TO 22.500KGS</t>
-  </si>
-  <si>
-    <t>CAP FORGE(2TONNE HAMMER)</t>
-  </si>
-  <si>
-    <t>SEAT RING(2TONNE HAMMER)</t>
-  </si>
-  <si>
-    <t>200 RCS A105</t>
-  </si>
-  <si>
-    <t>PRODUCTION PLANNING 6.25 TONNE AS ON DATE 04.05.2026</t>
-  </si>
-  <si>
-    <t>3PCS SAMPLING 90 DIA 4130 CUT WT 7.150 TO 7.350KGS</t>
-  </si>
-  <si>
-    <t>3+2PCS SAMPLING 200 RCS A105/200 RCS 4130 CUT WT 140 TO 146KGS</t>
+    <t>50pcs(1st shipment)UNDER FORGING OK 200PCS</t>
+  </si>
+  <si>
+    <t>30pcs(1st shipment) FORGING OK 100PCS</t>
+  </si>
+  <si>
+    <t>PRODUCTION PLANNING 6.25 TONNE AS ON DATE 05.07.2026</t>
+  </si>
+  <si>
+    <t>114.3/'921MM</t>
+  </si>
+  <si>
+    <t>UNDER FORGING</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1477,15 +1771,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1580,7 +1881,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1646,13 +1947,34 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2001,7 +2323,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -2074,493 +2396,463 @@
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>86</v>
+        <v>266</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>85</v>
+        <v>269</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18" t="s">
-        <v>70</v>
+        <v>272</v>
       </c>
       <c r="G4" s="18">
-        <v>300</v>
-      </c>
-      <c r="H4" s="26">
-        <v>15.5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H4" s="26"/>
       <c r="I4" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="25" t="s">
-        <v>88</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>89</v>
+        <v>266</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>90</v>
+        <v>268</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>91</v>
+        <v>270</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18" t="s">
-        <v>70</v>
+        <v>272</v>
       </c>
       <c r="G5" s="18">
         <v>50</v>
       </c>
-      <c r="H5" s="26">
-        <v>116</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>92</v>
+      <c r="H5" s="26"/>
+      <c r="I5" s="18">
+        <v>4130</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>309</v>
+        <v>380</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="G6" s="18">
         <v>50</v>
       </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="18">
-        <v>4130</v>
+      <c r="H6" s="26">
+        <v>88.5</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>166</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>309</v>
+        <v>380</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>311</v>
+        <v>376</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="G7" s="18">
         <v>50</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="26">
+        <v>88.5</v>
+      </c>
       <c r="I7" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="J7" s="25"/>
-    </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>315</v>
+        <v>455</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18" t="s">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="G8" s="18">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H8" s="26"/>
-      <c r="I8" s="18">
-        <v>4130</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I8" s="18"/>
+      <c r="J8" s="25"/>
+    </row>
+    <row r="9" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>312</v>
+        <v>453</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>316</v>
+        <v>456</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18" t="s">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="G9" s="18">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H9" s="26"/>
-      <c r="I9" s="18">
-        <v>4130</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="18"/>
+      <c r="J9" s="25"/>
+    </row>
+    <row r="10" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>309</v>
+        <v>451</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>317</v>
+        <v>457</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18" t="s">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="G10" s="18">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H10" s="26"/>
-      <c r="I10" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="I10" s="18"/>
+      <c r="J10" s="25"/>
+    </row>
+    <row r="11" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>222</v>
+        <v>424</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>224</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18" t="s">
-        <v>72</v>
+        <v>427</v>
       </c>
       <c r="G11" s="18">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H11" s="26">
-        <v>37.25</v>
+        <v>81</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>76</v>
+        <v>428</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>222</v>
+        <v>424</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>226</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18" t="s">
-        <v>72</v>
+        <v>427</v>
       </c>
       <c r="G12" s="18">
-        <v>50</v>
-      </c>
-      <c r="H12" s="26">
-        <v>41</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H12" s="26"/>
       <c r="I12" s="18" t="s">
-        <v>76</v>
+        <v>428</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>398</v>
+        <v>429</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>308</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18" t="s">
-        <v>107</v>
+        <v>427</v>
       </c>
       <c r="G13" s="18">
-        <v>275</v>
-      </c>
-      <c r="H13" s="26">
-        <v>141</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>447</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="H13" s="26"/>
+      <c r="I13" s="18"/>
       <c r="J13" s="25" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>68</v>
+        <v>505</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>429</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>68</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
-    </row>
-    <row r="16" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="14">
-        <v>250</v>
-      </c>
-      <c r="H16" s="14">
-        <v>7.75</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="G14" s="18">
+        <v>50</v>
+      </c>
+      <c r="H14" s="26"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="G15" s="18">
+        <v>400</v>
+      </c>
+      <c r="H15" s="26"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="G16" s="18">
+        <v>449</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="17" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>73</v>
+        <v>429</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>74</v>
+        <v>434</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>75</v>
+        <v>506</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>77</v>
+        <v>427</v>
+      </c>
+      <c r="G17" s="18">
+        <v>250</v>
+      </c>
+      <c r="H17" s="26">
+        <v>26.5</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J17" s="25" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="17" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>247</v>
+        <v>429</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>435</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>248</v>
+        <v>507</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18" t="s">
-        <v>246</v>
+        <v>427</v>
       </c>
       <c r="G18" s="18">
-        <v>200</v>
-      </c>
-      <c r="H18" s="28">
-        <v>23</v>
+        <v>250</v>
+      </c>
+      <c r="H18" s="26">
+        <v>27.25</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>249</v>
+        <v>86</v>
       </c>
       <c r="J18" s="25" t="s">
-        <v>15</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>396</v>
+        <v>436</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>397</v>
+        <v>508</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="18" t="s">
-        <v>72</v>
+        <v>427</v>
       </c>
       <c r="G19" s="18">
-        <v>300</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>850</v>
+      </c>
+      <c r="H19" s="26">
+        <v>17.75</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>399</v>
+        <v>441</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>400</v>
+        <v>442</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="18" t="s">
-        <v>72</v>
+        <v>444</v>
       </c>
       <c r="G20" s="18">
-        <v>30</v>
-      </c>
-      <c r="H20" s="18">
-        <v>22.3</v>
+        <v>350</v>
+      </c>
+      <c r="H20" s="26">
+        <v>23.1</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>108</v>
+        <v>445</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18" t="s">
-        <v>72</v>
+        <v>462</v>
       </c>
       <c r="G21" s="18">
-        <v>120</v>
-      </c>
-      <c r="H21" s="18">
-        <v>22.3</v>
+        <v>400</v>
+      </c>
+      <c r="H21" s="26">
+        <v>57</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>443</v>
+        <v>428</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
@@ -2568,27 +2860,27 @@
         <v>72</v>
       </c>
       <c r="G22" s="18">
-        <v>160</v>
-      </c>
-      <c r="H22" s="18">
-        <v>18.649999999999999</v>
+        <v>110</v>
+      </c>
+      <c r="H22" s="26">
+        <v>27.25</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>15</v>
+        <v>475</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>435</v>
+        <v>499</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
@@ -2596,75 +2888,83 @@
         <v>72</v>
       </c>
       <c r="G23" s="18">
+        <v>300</v>
+      </c>
+      <c r="H23" s="26">
         <v>30</v>
       </c>
-      <c r="H23" s="18">
-        <v>22.2</v>
-      </c>
       <c r="I23" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>68</v>
+    <row r="24" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>500</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>68</v>
+        <v>496</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>68</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>68</v>
+        <v>72</v>
+      </c>
+      <c r="G24" s="18">
+        <v>160</v>
+      </c>
+      <c r="H24" s="26">
+        <v>30</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
+        <v>83</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>498</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="18">
+        <v>80</v>
+      </c>
+      <c r="H25" s="26">
+        <v>31.25</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
-        <v>252</v>
+        <v>501</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>253</v>
+        <v>502</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>183</v>
+        <v>503</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
@@ -2672,27 +2972,27 @@
         <v>72</v>
       </c>
       <c r="G26" s="18">
-        <v>80</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>254</v>
+        <v>95</v>
+      </c>
+      <c r="H26" s="26">
+        <v>46.5</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>15</v>
+        <v>509</v>
+      </c>
+      <c r="J26" s="25" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
-        <v>402</v>
+        <v>511</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>80</v>
+        <v>515</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>81</v>
+        <v>516</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
@@ -2700,277 +3000,746 @@
         <v>70</v>
       </c>
       <c r="G27" s="18">
+        <v>160</v>
+      </c>
+      <c r="H27" s="26">
+        <v>95</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="29" t="s">
+        <v>540</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>526</v>
+      </c>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="H28" s="33">
+        <v>17.75</v>
+      </c>
+      <c r="I28" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="J28" s="29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="30">
+        <v>50</v>
+      </c>
+      <c r="H29" s="33">
+        <v>116</v>
+      </c>
+      <c r="I29" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="29"/>
+    </row>
+    <row r="30" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24"/>
+    </row>
+    <row r="32" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="14">
+        <v>250</v>
+      </c>
+      <c r="H32" s="14">
+        <v>7.75</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="G33" s="18">
+        <v>50</v>
+      </c>
+      <c r="H33" s="26"/>
+      <c r="I33" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="J33" s="25" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="11">
+        <v>50</v>
+      </c>
+      <c r="H34" s="11">
+        <v>20</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="11">
+        <v>200</v>
+      </c>
+      <c r="H35" s="11">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>480</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="11">
+        <v>80</v>
+      </c>
+      <c r="H36" s="11">
+        <v>18.8</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="11">
+        <v>150</v>
+      </c>
+      <c r="H37" s="11">
+        <v>22.85</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>489</v>
+      </c>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="11">
+        <v>200</v>
+      </c>
+      <c r="H38" s="11">
+        <v>22.3</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>491</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="11">
+        <v>180</v>
+      </c>
+      <c r="H39" s="11">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G40" s="11">
+        <v>100</v>
+      </c>
+      <c r="H40" s="11">
+        <v>20.75</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>519</v>
+      </c>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="11">
+        <v>500</v>
+      </c>
+      <c r="H41" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" s="11">
+        <v>600</v>
+      </c>
+      <c r="H42" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A43" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="C43" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G43" s="34">
+        <v>195</v>
+      </c>
+      <c r="H43" s="34">
+        <v>11</v>
+      </c>
+      <c r="I43" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="J43" s="34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+    </row>
+    <row r="45" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="21"/>
+    </row>
+    <row r="47" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
+        <v>463</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G47" s="18">
         <v>300</v>
       </c>
-      <c r="H27" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="J27" s="18" t="s">
+      <c r="H47" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J47" s="18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-    </row>
-    <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-    </row>
-    <row r="41" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-    </row>
-    <row r="43" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-    </row>
-    <row r="44" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-    </row>
-    <row r="45" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-    </row>
-    <row r="46" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-    </row>
-    <row r="47" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-    </row>
-    <row r="50" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-    </row>
-    <row r="52" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:10" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G48" s="18">
+        <v>500</v>
+      </c>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="J48" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G49" s="18">
+        <v>160</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G50" s="18">
+        <v>500</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J50" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>534</v>
+      </c>
+      <c r="C51" s="36" t="s">
+        <v>536</v>
+      </c>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="G51" s="18">
+        <v>100</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="I51" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="J51" s="18" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>537</v>
+      </c>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="G52" s="18">
+        <v>30</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>539</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I54" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J54" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="56" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="16"/>
@@ -3068,7 +3837,7 @@
       <c r="J86" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:J54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -3095,19 +3864,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="39"/>
     </row>
     <row r="2" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3143,19 +3912,19 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="35"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="42"/>
     </row>
     <row r="4" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -3193,19 +3962,19 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -3652,7 +4421,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="15" customWidth="1"/>
@@ -3663,12 +4432,12 @@
     <col min="7" max="7" width="10.5703125" style="15" customWidth="1"/>
     <col min="8" max="8" width="12" style="15" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="54.7109375" style="15" customWidth="1"/>
+    <col min="10" max="10" width="52.85546875" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
-        <v>448</v>
+        <v>546</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -3711,18 +4480,18 @@
     </row>
     <row r="3" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="18"/>
       <c r="F3" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G3" s="18">
         <v>225</v>
@@ -3731,562 +4500,562 @@
         <v>42.25</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>99</v>
+        <v>261</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>100</v>
+        <v>354</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G4" s="18">
-        <v>300</v>
+        <v>76</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="H4" s="26">
-        <v>17.5</v>
+        <v>28.5</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="J4" s="25" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>103</v>
+        <v>355</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G5" s="18">
-        <v>200</v>
+        <v>76</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="H5" s="26">
-        <v>12.1</v>
+        <v>28</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>114</v>
+        <v>354</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G6" s="18">
-        <v>1875</v>
+        <v>76</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>265</v>
       </c>
       <c r="H6" s="26">
-        <v>7.95</v>
+        <v>28.5</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>394</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>115</v>
+        <v>264</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>119</v>
+        <v>355</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G7" s="18">
-        <v>600</v>
+        <v>76</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>265</v>
       </c>
       <c r="H7" s="26">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>429</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G8" s="18">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="H8" s="26">
-        <v>23.5</v>
+        <v>17.5</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>83</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>433</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>117</v>
+        <v>254</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>121</v>
+        <v>327</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G9" s="18">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="H9" s="26">
-        <v>12.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>420</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="18"/>
+        <v>255</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>328</v>
+      </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G10" s="18">
-        <v>20</v>
-      </c>
-      <c r="H10" s="26"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="25"/>
+        <v>50</v>
+      </c>
+      <c r="H10" s="26">
+        <v>18.3</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="11" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>118</v>
+        <v>256</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>122</v>
+        <v>327</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="18">
-        <v>100</v>
+        <v>76</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="H11" s="26">
-        <v>24.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>434</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="18">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="H12" s="26">
-        <v>42</v>
+        <v>18.3</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>219</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>251</v>
+        <v>327</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="18">
-        <v>250</v>
+        <v>76</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="H13" s="26">
-        <v>46.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="18">
-        <v>50</v>
+        <v>76</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="H14" s="26">
-        <v>18.899999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>385</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>296</v>
+        <v>84</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>378</v>
+        <v>85</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G15" s="18">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H15" s="26">
-        <v>18.3</v>
+        <v>12.1</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>385</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>377</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>168</v>
+        <v>76</v>
+      </c>
+      <c r="G16" s="18">
+        <v>1875</v>
       </c>
       <c r="H16" s="26">
-        <v>18.899999999999999</v>
+        <v>7.95</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>386</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>298</v>
+        <v>96</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>378</v>
+        <v>100</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>168</v>
+        <v>76</v>
+      </c>
+      <c r="G17" s="18">
+        <v>600</v>
       </c>
       <c r="H17" s="26">
-        <v>18.3</v>
+        <v>14.5</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="25" t="s">
-        <v>386</v>
+        <v>74</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>299</v>
+        <v>97</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>377</v>
+        <v>101</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>301</v>
+        <v>76</v>
+      </c>
+      <c r="G18" s="18">
+        <v>225</v>
       </c>
       <c r="H18" s="26">
-        <v>18.899999999999999</v>
+        <v>23.5</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>387</v>
+        <v>73</v>
+      </c>
+      <c r="J18" s="29" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>378</v>
+        <v>102</v>
       </c>
       <c r="D19" s="18"/>
       <c r="E19" s="18"/>
       <c r="F19" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>301</v>
+        <v>76</v>
+      </c>
+      <c r="G19" s="18">
+        <v>320</v>
       </c>
       <c r="H19" s="26">
-        <v>18.3</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="J19" s="25" t="s">
-        <v>387</v>
+        <v>74</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>417</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C20" s="18"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18"/>
       <c r="F20" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="H20" s="26">
-        <v>28.5</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J20" s="25" t="s">
-        <v>390</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G20" s="18">
+        <v>20</v>
+      </c>
+      <c r="H20" s="26"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>303</v>
+        <v>99</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>418</v>
+        <v>103</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>168</v>
+        <v>76</v>
+      </c>
+      <c r="G21" s="18">
+        <v>100</v>
       </c>
       <c r="H21" s="26">
-        <v>28</v>
+        <v>24.5</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>390</v>
+        <v>73</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>304</v>
+        <v>93</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>417</v>
+        <v>91</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>306</v>
+        <v>76</v>
+      </c>
+      <c r="G22" s="18">
+        <v>70</v>
       </c>
       <c r="H22" s="26">
-        <v>28.5</v>
+        <v>42</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>391</v>
+        <v>92</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>305</v>
+        <v>212</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>418</v>
+        <v>213</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>306</v>
+        <v>76</v>
+      </c>
+      <c r="G23" s="18">
+        <v>250</v>
       </c>
       <c r="H23" s="26">
-        <v>28</v>
+        <v>46.5</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>391</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4339,10 +5108,10 @@
     </row>
     <row r="26" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>11</v>
@@ -4350,2783 +5119,2999 @@
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G26" s="18">
         <v>1660</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="27">
         <v>7.9</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>405</v>
+        <v>341</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
       <c r="F27" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G27" s="18">
         <v>800</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="27">
         <v>1</v>
       </c>
       <c r="I27" s="18"/>
       <c r="J27" s="25" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G28" s="18">
         <v>200</v>
       </c>
-      <c r="H28" s="28"/>
+      <c r="H28" s="27"/>
       <c r="I28" s="18"/>
       <c r="J28" s="25" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>327</v>
+        <v>281</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G29" s="18">
         <v>200</v>
       </c>
-      <c r="H29" s="28"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="25" t="s">
-        <v>216</v>
+      <c r="H29" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="J29" s="29" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>326</v>
+        <v>280</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>328</v>
+        <v>282</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G30" s="18">
         <v>200</v>
       </c>
-      <c r="H30" s="28"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="25" t="s">
-        <v>216</v>
+      <c r="H30" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
       <c r="E31" s="18"/>
       <c r="F31" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G31" s="18">
         <v>250</v>
       </c>
-      <c r="H31" s="28"/>
+      <c r="H31" s="27"/>
       <c r="I31" s="18"/>
       <c r="J31" s="25" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="D32" s="18"/>
       <c r="E32" s="18"/>
       <c r="F32" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G32" s="18">
         <v>200</v>
       </c>
-      <c r="H32" s="28"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="25" t="s">
-        <v>216</v>
+      <c r="H32" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>331</v>
+        <v>285</v>
       </c>
       <c r="D33" s="18"/>
       <c r="E33" s="18"/>
       <c r="F33" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G33" s="18">
         <v>200</v>
       </c>
-      <c r="H33" s="28"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="25" t="s">
-        <v>216</v>
+      <c r="H33" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>332</v>
+        <v>286</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>330</v>
+        <v>284</v>
       </c>
       <c r="D34" s="18"/>
       <c r="E34" s="18"/>
       <c r="F34" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G34" s="18">
         <v>50</v>
       </c>
-      <c r="H34" s="28"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="25" t="s">
-        <v>216</v>
+      <c r="H34" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="J34" s="29" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>331</v>
+        <v>285</v>
       </c>
       <c r="D35" s="18"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G35" s="18">
         <v>50</v>
       </c>
-      <c r="H35" s="28"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="25" t="s">
-        <v>216</v>
+      <c r="H35" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="J35" s="29" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="5" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D36" s="18"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G36" s="18">
         <v>1400</v>
       </c>
-      <c r="H36" s="28">
+      <c r="H36" s="27">
         <v>2.2000000000000002</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>392</v>
+        <v>215</v>
+      </c>
+      <c r="J36" s="29" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>410</v>
+        <v>347</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="D37" s="18"/>
       <c r="E37" s="18"/>
       <c r="F37" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G37" s="18">
         <v>300</v>
       </c>
-      <c r="H37" s="28">
+      <c r="H37" s="27">
         <v>1.85</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="J37" s="25" t="s">
-        <v>427</v>
+        <v>353</v>
+      </c>
+      <c r="J37" s="29" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>411</v>
+        <v>348</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>415</v>
+        <v>352</v>
       </c>
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G38" s="18">
         <v>300</v>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="27">
         <v>1.95</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="J38" s="25" t="s">
-        <v>427</v>
+        <v>353</v>
+      </c>
+      <c r="J38" s="29" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>412</v>
+        <v>349</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G39" s="18">
         <v>200</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="27">
         <v>1.85</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="J39" s="25" t="s">
-        <v>428</v>
+        <v>353</v>
+      </c>
+      <c r="J39" s="29" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>415</v>
+        <v>352</v>
       </c>
       <c r="D40" s="18"/>
       <c r="E40" s="18"/>
       <c r="F40" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G40" s="18">
         <v>200</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="27">
         <v>1.95</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="J40" s="25" t="s">
-        <v>428</v>
+        <v>353</v>
+      </c>
+      <c r="J40" s="29" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="18"/>
+        <v>117</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>408</v>
+      </c>
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G41" s="18">
         <v>200</v>
       </c>
-      <c r="H41" s="28"/>
+      <c r="H41" s="27"/>
       <c r="I41" s="18"/>
       <c r="J41" s="25" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>140</v>
+        <v>409</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>412</v>
       </c>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G42" s="18">
-        <v>1650</v>
-      </c>
-      <c r="H42" s="28">
-        <v>6.55</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>257</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H42" s="27"/>
+      <c r="I42" s="18"/>
       <c r="J42" s="25" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>146</v>
+        <v>410</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>413</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G43" s="18">
         <v>200</v>
       </c>
-      <c r="H43" s="29">
-        <v>8</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>257</v>
-      </c>
+      <c r="H43" s="27"/>
+      <c r="I43" s="18"/>
       <c r="J43" s="25" t="s">
-        <v>219</v>
+        <v>411</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G44" s="18">
-        <v>800</v>
-      </c>
-      <c r="H44" s="28">
-        <v>1.65</v>
-      </c>
-      <c r="I44" s="18"/>
+        <v>1650</v>
+      </c>
+      <c r="H44" s="27">
+        <v>6.55</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>216</v>
+      </c>
       <c r="J44" s="25" t="s">
-        <v>155</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="D45" s="18"/>
       <c r="E45" s="18"/>
       <c r="F45" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G45" s="18">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H45" s="28">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I45" s="18"/>
-      <c r="J45" s="25" t="s">
-        <v>156</v>
+        <v>8</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="J45" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>321</v>
+        <v>132</v>
       </c>
       <c r="D46" s="18"/>
       <c r="E46" s="18"/>
       <c r="F46" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G46" s="18">
-        <v>200</v>
-      </c>
-      <c r="H46" s="28"/>
+        <v>800</v>
+      </c>
+      <c r="H46" s="27">
+        <v>1.65</v>
+      </c>
       <c r="I46" s="18"/>
       <c r="J46" s="25" t="s">
-        <v>345</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>199</v>
+        <v>129</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>322</v>
+        <v>133</v>
       </c>
       <c r="D47" s="18"/>
       <c r="E47" s="18"/>
       <c r="F47" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G47" s="18">
-        <v>200</v>
-      </c>
-      <c r="H47" s="28"/>
+        <v>400</v>
+      </c>
+      <c r="H47" s="27">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="I47" s="18"/>
       <c r="J47" s="25" t="s">
-        <v>345</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>335</v>
+        <v>174</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>337</v>
+        <v>275</v>
       </c>
       <c r="D48" s="18"/>
       <c r="E48" s="18"/>
       <c r="F48" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G48" s="18">
         <v>200</v>
       </c>
-      <c r="H48" s="28"/>
+      <c r="H48" s="27"/>
       <c r="I48" s="18"/>
       <c r="J48" s="25" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>338</v>
+        <v>276</v>
       </c>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G49" s="18">
         <v>200</v>
       </c>
-      <c r="H49" s="28"/>
+      <c r="H49" s="27"/>
       <c r="I49" s="18"/>
       <c r="J49" s="25" t="s">
-        <v>345</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>149</v>
+        <v>289</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="D50" s="18"/>
       <c r="E50" s="18"/>
       <c r="F50" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G50" s="18">
-        <v>275</v>
-      </c>
-      <c r="H50" s="28">
-        <v>6.75</v>
-      </c>
-      <c r="I50" s="18" t="s">
-        <v>127</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H50" s="27"/>
+      <c r="I50" s="18"/>
       <c r="J50" s="25" t="s">
-        <v>389</v>
+        <v>298</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>200</v>
+        <v>292</v>
       </c>
       <c r="D51" s="18"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G51" s="18">
         <v>200</v>
       </c>
-      <c r="H51" s="28">
-        <v>3.5</v>
-      </c>
-      <c r="I51" s="18" t="s">
-        <v>163</v>
-      </c>
+      <c r="H51" s="27"/>
+      <c r="I51" s="18"/>
       <c r="J51" s="25" t="s">
-        <v>431</v>
+        <v>298</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>
       <c r="F52" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G52" s="18">
-        <v>200</v>
-      </c>
-      <c r="H52" s="28">
-        <v>4.4000000000000004</v>
+        <v>275</v>
+      </c>
+      <c r="H52" s="27">
+        <v>6.75</v>
       </c>
       <c r="I52" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="J52" s="25" t="s">
-        <v>431</v>
+        <v>108</v>
+      </c>
+      <c r="J52" s="29" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>343</v>
+        <v>178</v>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="18"/>
       <c r="F53" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G53" s="18">
-        <v>75</v>
-      </c>
-      <c r="H53" s="28">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="H53" s="27">
+        <v>3.5</v>
       </c>
       <c r="I53" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="J53" s="25" t="s">
-        <v>432</v>
+        <v>144</v>
+      </c>
+      <c r="J53" s="29" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>344</v>
+        <v>179</v>
       </c>
       <c r="D54" s="18"/>
       <c r="E54" s="18"/>
       <c r="F54" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G54" s="18">
-        <v>75</v>
-      </c>
-      <c r="H54" s="28">
-        <v>4.5</v>
+        <v>200</v>
+      </c>
+      <c r="H54" s="27">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I54" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="J54" s="25" t="s">
-        <v>432</v>
+        <v>144</v>
+      </c>
+      <c r="J54" s="29" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>150</v>
+        <v>295</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="18"/>
       <c r="F55" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G55" s="18">
-        <v>850</v>
-      </c>
-      <c r="H55" s="28">
-        <v>10.65</v>
+        <v>75</v>
+      </c>
+      <c r="H55" s="27">
+        <v>3</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="J55" s="25" t="s">
-        <v>383</v>
+        <v>144</v>
+      </c>
+      <c r="J55" s="29" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="D56" s="18"/>
       <c r="E56" s="18"/>
       <c r="F56" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G56" s="18">
-        <v>200</v>
-      </c>
-      <c r="H56" s="28">
-        <v>5.9</v>
+        <v>75</v>
+      </c>
+      <c r="H56" s="27">
+        <v>4.5</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J56" s="25" t="s">
-        <v>424</v>
+        <v>144</v>
+      </c>
+      <c r="J56" s="29" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>347</v>
+        <v>131</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="D57" s="18"/>
       <c r="E57" s="18"/>
       <c r="F57" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G57" s="18">
-        <v>200</v>
-      </c>
-      <c r="H57" s="28">
-        <v>7.4</v>
+        <v>850</v>
+      </c>
+      <c r="H57" s="27">
+        <v>10.65</v>
       </c>
       <c r="I57" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J57" s="25" t="s">
-        <v>108</v>
+        <v>223</v>
+      </c>
+      <c r="J57" s="29" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>352</v>
+        <v>180</v>
       </c>
       <c r="D58" s="18"/>
       <c r="E58" s="18"/>
       <c r="F58" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G58" s="18">
-        <v>400</v>
-      </c>
-      <c r="H58" s="28">
-        <v>5.6</v>
+        <v>200</v>
+      </c>
+      <c r="H58" s="27">
+        <v>5.9</v>
       </c>
       <c r="I58" s="18" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>421</v>
+        <v>384</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>353</v>
+        <v>181</v>
       </c>
       <c r="D59" s="18"/>
       <c r="E59" s="18"/>
       <c r="F59" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G59" s="18">
-        <v>400</v>
-      </c>
-      <c r="H59" s="28">
-        <v>6.1</v>
+        <v>200</v>
+      </c>
+      <c r="H59" s="27">
+        <v>7.4</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>421</v>
+        <v>385</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>352</v>
+        <v>305</v>
       </c>
       <c r="D60" s="18"/>
       <c r="E60" s="18"/>
       <c r="F60" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G60" s="18">
-        <v>150</v>
-      </c>
-      <c r="H60" s="28">
+        <v>400</v>
+      </c>
+      <c r="H60" s="27">
         <v>5.6</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J60" s="25" t="s">
-        <v>422</v>
+        <v>108</v>
+      </c>
+      <c r="J60" s="29" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>353</v>
+        <v>306</v>
       </c>
       <c r="D61" s="18"/>
       <c r="E61" s="18"/>
       <c r="F61" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G61" s="18">
-        <v>150</v>
-      </c>
-      <c r="H61" s="28">
+        <v>400</v>
+      </c>
+      <c r="H61" s="27">
         <v>6.1</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J61" s="25" t="s">
-        <v>422</v>
+        <v>108</v>
+      </c>
+      <c r="J61" s="29" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>352</v>
+        <v>305</v>
       </c>
       <c r="D62" s="18"/>
       <c r="E62" s="18"/>
       <c r="F62" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G62" s="18">
-        <v>50</v>
-      </c>
-      <c r="H62" s="28">
+        <v>150</v>
+      </c>
+      <c r="H62" s="27">
         <v>5.6</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J62" s="25" t="s">
-        <v>423</v>
+        <v>108</v>
+      </c>
+      <c r="J62" s="29" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>353</v>
+        <v>306</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
       <c r="F63" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G63" s="18">
-        <v>50</v>
-      </c>
-      <c r="H63" s="28">
+        <v>150</v>
+      </c>
+      <c r="H63" s="27">
         <v>6.1</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J63" s="25" t="s">
-        <v>423</v>
+        <v>108</v>
+      </c>
+      <c r="J63" s="29" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B64" s="18" t="s">
-        <v>204</v>
+        <v>77</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>307</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="D64" s="18"/>
       <c r="E64" s="18"/>
       <c r="F64" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G64" s="18">
-        <v>100</v>
-      </c>
-      <c r="H64" s="28">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="H64" s="27">
+        <v>5.6</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J64" s="25" t="s">
-        <v>215</v>
+        <v>108</v>
+      </c>
+      <c r="J64" s="29" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>205</v>
+        <v>77</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>308</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="D65" s="18"/>
       <c r="E65" s="18"/>
       <c r="F65" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G65" s="18">
-        <v>100</v>
-      </c>
-      <c r="H65" s="28">
-        <v>10.75</v>
+        <v>50</v>
+      </c>
+      <c r="H65" s="27">
+        <v>6.1</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>215</v>
+        <v>108</v>
+      </c>
+      <c r="J65" s="29" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>406</v>
+        <v>182</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>358</v>
+        <v>184</v>
       </c>
       <c r="D66" s="18"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G66" s="18">
-        <v>250</v>
-      </c>
-      <c r="H66" s="28"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="25"/>
+        <v>100</v>
+      </c>
+      <c r="H66" s="27">
+        <v>10</v>
+      </c>
+      <c r="I66" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J66" s="29" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>407</v>
+        <v>183</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>359</v>
+        <v>185</v>
       </c>
       <c r="D67" s="18"/>
       <c r="E67" s="18"/>
       <c r="F67" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G67" s="18">
-        <v>250</v>
-      </c>
-      <c r="H67" s="28"/>
-      <c r="I67" s="18"/>
-      <c r="J67" s="25"/>
+        <v>100</v>
+      </c>
+      <c r="H67" s="27">
+        <v>11.1</v>
+      </c>
+      <c r="I67" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J67" s="29" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="68" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="D68" s="18"/>
       <c r="E68" s="18"/>
       <c r="F68" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G68" s="18">
-        <v>100</v>
-      </c>
-      <c r="H68" s="28"/>
-      <c r="I68" s="18"/>
-      <c r="J68" s="25"/>
+        <v>250</v>
+      </c>
+      <c r="H68" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="I68" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J68" s="29" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>409</v>
+        <v>344</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
       <c r="D69" s="18"/>
       <c r="E69" s="18"/>
       <c r="F69" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G69" s="18">
-        <v>100</v>
-      </c>
-      <c r="H69" s="28"/>
-      <c r="I69" s="18"/>
-      <c r="J69" s="25"/>
+        <v>250</v>
+      </c>
+      <c r="H69" s="27">
+        <v>9.4</v>
+      </c>
+      <c r="I69" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J69" s="29" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>358</v>
+        <v>311</v>
       </c>
       <c r="D70" s="18"/>
       <c r="E70" s="18"/>
       <c r="F70" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G70" s="18">
         <v>100</v>
       </c>
-      <c r="H70" s="28"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="25"/>
+      <c r="H70" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="I70" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J70" s="29" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>359</v>
+        <v>312</v>
       </c>
       <c r="D71" s="18"/>
       <c r="E71" s="18"/>
       <c r="F71" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G71" s="18">
         <v>100</v>
       </c>
-      <c r="H71" s="28"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="25"/>
+      <c r="H71" s="27">
+        <v>9.4</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J71" s="29" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="D72" s="18"/>
       <c r="E72" s="18"/>
       <c r="F72" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G72" s="18">
-        <v>200</v>
-      </c>
-      <c r="H72" s="28"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="25"/>
+        <v>100</v>
+      </c>
+      <c r="H72" s="27">
+        <v>8.5</v>
+      </c>
+      <c r="I72" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J72" s="29" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G73" s="18">
-        <v>200</v>
-      </c>
-      <c r="H73" s="28"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="25"/>
+        <v>100</v>
+      </c>
+      <c r="H73" s="27">
+        <v>9.4</v>
+      </c>
+      <c r="I73" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J73" s="29" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B74" s="25" t="s">
-        <v>157</v>
+        <v>77</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>313</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>158</v>
+        <v>315</v>
       </c>
       <c r="D74" s="18"/>
       <c r="E74" s="18"/>
       <c r="F74" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G74" s="18">
-        <v>50</v>
-      </c>
-      <c r="H74" s="28">
-        <v>8.1</v>
+        <v>200</v>
+      </c>
+      <c r="H74" s="27">
+        <v>11.5</v>
       </c>
       <c r="I74" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="J74" s="25" t="s">
-        <v>219</v>
+        <v>87</v>
+      </c>
+      <c r="J74" s="29" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B75" s="25" t="s">
-        <v>368</v>
+        <v>77</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>314</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>370</v>
+        <v>316</v>
       </c>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G75" s="18">
-        <v>20</v>
-      </c>
-      <c r="H75" s="28"/>
-      <c r="I75" s="18"/>
-      <c r="J75" s="25"/>
+        <v>200</v>
+      </c>
+      <c r="H75" s="27">
+        <v>12</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J75" s="29" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>369</v>
+        <v>138</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>371</v>
+        <v>139</v>
       </c>
       <c r="D76" s="18"/>
       <c r="E76" s="18"/>
       <c r="F76" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G76" s="18">
-        <v>20</v>
-      </c>
-      <c r="H76" s="28"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="25"/>
+        <v>50</v>
+      </c>
+      <c r="H76" s="27">
+        <v>8.1</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="J76" s="29" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="D77" s="18"/>
       <c r="E77" s="18"/>
       <c r="F77" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G77" s="18">
-        <v>100</v>
-      </c>
-      <c r="H77" s="28"/>
+        <v>20</v>
+      </c>
+      <c r="H77" s="27"/>
       <c r="I77" s="18"/>
-      <c r="J77" s="25" t="s">
-        <v>215</v>
-      </c>
+      <c r="J77" s="25"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="D78" s="18"/>
       <c r="E78" s="18"/>
       <c r="F78" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G78" s="18">
-        <v>100</v>
-      </c>
-      <c r="H78" s="28"/>
+        <v>20</v>
+      </c>
+      <c r="H78" s="27"/>
       <c r="I78" s="18"/>
-      <c r="J78" s="25" t="s">
-        <v>215</v>
-      </c>
+      <c r="J78" s="25"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>123</v>
+        <v>317</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>125</v>
+        <v>319</v>
       </c>
       <c r="D79" s="18"/>
       <c r="E79" s="18"/>
       <c r="F79" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G79" s="18">
-        <v>200</v>
-      </c>
-      <c r="H79" s="28">
-        <v>5.0999999999999996</v>
+        <v>100</v>
+      </c>
+      <c r="H79" s="27">
+        <v>14</v>
       </c>
       <c r="I79" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J79" s="25" t="s">
-        <v>219</v>
+        <v>74</v>
+      </c>
+      <c r="J79" s="29" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>124</v>
+        <v>318</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>126</v>
+        <v>320</v>
       </c>
       <c r="D80" s="18"/>
       <c r="E80" s="18"/>
       <c r="F80" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G80" s="18">
-        <v>200</v>
-      </c>
-      <c r="H80" s="28">
-        <v>5.9</v>
+        <v>100</v>
+      </c>
+      <c r="H80" s="27">
+        <v>13.5</v>
       </c>
       <c r="I80" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J80" s="25" t="s">
-        <v>372</v>
+        <v>74</v>
+      </c>
+      <c r="J80" s="29" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="D81" s="18"/>
       <c r="E81" s="18"/>
       <c r="F81" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G81" s="18">
-        <v>450</v>
-      </c>
-      <c r="H81" s="28">
-        <v>4.75</v>
-      </c>
-      <c r="I81" s="18"/>
-      <c r="J81" s="25"/>
+        <v>200</v>
+      </c>
+      <c r="H81" s="27">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J81" s="29" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="D82" s="18"/>
       <c r="E82" s="18"/>
       <c r="F82" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G82" s="18">
-        <v>450</v>
-      </c>
-      <c r="H82" s="28">
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="I82" s="18"/>
-      <c r="J82" s="25"/>
+        <v>200</v>
+      </c>
+      <c r="H82" s="27">
+        <v>5.9</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J82" s="29" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>173</v>
+        <v>111</v>
       </c>
       <c r="D83" s="18"/>
       <c r="E83" s="18"/>
       <c r="F83" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G83" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H83" s="28">
-        <v>9</v>
+        <v>76</v>
+      </c>
+      <c r="G83" s="18">
+        <v>450</v>
+      </c>
+      <c r="H83" s="27">
+        <v>4.75</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J83" s="25" t="s">
-        <v>219</v>
+        <v>144</v>
+      </c>
+      <c r="J83" s="29" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="D84" s="18"/>
       <c r="E84" s="18"/>
       <c r="F84" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G84" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="H84" s="28">
-        <v>9</v>
+        <v>76</v>
+      </c>
+      <c r="G84" s="18">
+        <v>450</v>
+      </c>
+      <c r="H84" s="27">
+        <v>4.75</v>
       </c>
       <c r="I84" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J84" s="25" t="s">
-        <v>220</v>
+        <v>108</v>
+      </c>
+      <c r="J84" s="29" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="D85" s="18"/>
       <c r="E85" s="18"/>
       <c r="F85" s="18" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="H85" s="28">
-        <v>13.2</v>
+        <v>155</v>
+      </c>
+      <c r="H85" s="27">
+        <v>9</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="J85" s="25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" s="9" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="J85" s="29" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>374</v>
+        <v>158</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="D86" s="18"/>
       <c r="E86" s="18"/>
       <c r="F86" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="H86" s="28">
-        <v>15.6</v>
+        <v>157</v>
+      </c>
+      <c r="H86" s="27">
+        <v>9</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J86" s="25" t="s">
-        <v>375</v>
+        <v>71</v>
+      </c>
+      <c r="J86" s="29" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D87" s="18"/>
       <c r="E87" s="18"/>
       <c r="F87" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G87" s="18">
-        <v>25</v>
-      </c>
-      <c r="H87" s="28">
+        <v>76</v>
+      </c>
+      <c r="G87" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H87" s="27">
         <v>13.2</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="J87" s="25" t="s">
-        <v>243</v>
+        <v>87</v>
+      </c>
+      <c r="J87" s="29" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A88" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="D88" s="18"/>
       <c r="E88" s="18"/>
       <c r="F88" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G88" s="18">
-        <v>25</v>
-      </c>
-      <c r="H88" s="28">
+        <v>76</v>
+      </c>
+      <c r="G88" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H88" s="27">
         <v>15.6</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="J88" s="25" t="s">
-        <v>375</v>
+        <v>74</v>
+      </c>
+      <c r="J88" s="29" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="18" t="s">
-        <v>208</v>
+        <v>77</v>
+      </c>
+      <c r="B89" s="25" t="s">
+        <v>161</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D89" s="18"/>
       <c r="E89" s="18"/>
       <c r="F89" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G89" s="18">
-        <v>200</v>
-      </c>
-      <c r="H89" s="28"/>
-      <c r="I89" s="18"/>
-      <c r="J89" s="25" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="H89" s="27">
+        <v>13.2</v>
+      </c>
+      <c r="I89" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="J89" s="29" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A90" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B90" s="18" t="s">
-        <v>209</v>
+        <v>77</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>325</v>
       </c>
       <c r="C90" s="18" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="18"/>
       <c r="F90" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G90" s="18">
-        <v>200</v>
-      </c>
-      <c r="H90" s="28"/>
-      <c r="I90" s="18"/>
-      <c r="J90" s="25" t="s">
-        <v>216</v>
+        <v>25</v>
+      </c>
+      <c r="H90" s="27">
+        <v>15.6</v>
+      </c>
+      <c r="I90" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="J90" s="29" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="C91" s="18" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="D91" s="18"/>
       <c r="E91" s="18"/>
       <c r="F91" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G91" s="18">
         <v>200</v>
       </c>
-      <c r="H91" s="28">
-        <v>5.4</v>
-      </c>
-      <c r="I91" s="18" t="s">
-        <v>71</v>
-      </c>
+      <c r="H91" s="27"/>
+      <c r="I91" s="18"/>
       <c r="J91" s="25" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>213</v>
+        <v>142</v>
       </c>
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G92" s="18">
         <v>200</v>
       </c>
-      <c r="H92" s="28">
-        <v>5</v>
-      </c>
-      <c r="I92" s="18" t="s">
-        <v>71</v>
-      </c>
+      <c r="H92" s="27"/>
+      <c r="I92" s="18"/>
       <c r="J92" s="25" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="D93" s="18"/>
       <c r="E93" s="18"/>
       <c r="F93" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G93" s="18">
-        <v>20</v>
-      </c>
-      <c r="H93" s="28">
-        <v>17</v>
+        <v>200</v>
+      </c>
+      <c r="H93" s="27">
+        <v>5.5</v>
       </c>
       <c r="I93" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="J93" s="25" t="s">
-        <v>219</v>
+        <v>71</v>
+      </c>
+      <c r="J93" s="29" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="C94" s="18" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="D94" s="18"/>
       <c r="E94" s="18"/>
       <c r="F94" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G94" s="18">
-        <v>20</v>
-      </c>
-      <c r="H94" s="28">
-        <v>18.899999999999999</v>
+        <v>200</v>
+      </c>
+      <c r="H94" s="27">
+        <v>5</v>
       </c>
       <c r="I94" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J94" s="25" t="s">
-        <v>219</v>
+        <v>71</v>
+      </c>
+      <c r="J94" s="29" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>265</v>
+        <v>203</v>
       </c>
       <c r="C95" s="18" t="s">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="D95" s="18"/>
       <c r="E95" s="18"/>
       <c r="F95" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G95" s="18">
-        <v>1050</v>
-      </c>
-      <c r="H95" s="28">
-        <v>5.0999999999999996</v>
+        <v>20</v>
+      </c>
+      <c r="H95" s="27">
+        <v>17</v>
       </c>
       <c r="I95" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J95" s="25" t="s">
-        <v>419</v>
+        <v>87</v>
+      </c>
+      <c r="J95" s="29" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B96" s="18" t="s">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="C96" s="18" t="s">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="D96" s="18"/>
       <c r="E96" s="18"/>
       <c r="F96" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G96" s="18">
-        <v>1050</v>
-      </c>
-      <c r="H96" s="28">
-        <v>5.0999999999999996</v>
+        <v>20</v>
+      </c>
+      <c r="H96" s="27">
+        <v>18.899999999999999</v>
       </c>
       <c r="I96" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J96" s="25" t="s">
-        <v>384</v>
+        <v>74</v>
+      </c>
+      <c r="J96" s="29" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="D97" s="18"/>
       <c r="E97" s="18"/>
       <c r="F97" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G97" s="18">
-        <v>600</v>
-      </c>
-      <c r="H97" s="28">
-        <v>4.4000000000000004</v>
+        <v>1050</v>
+      </c>
+      <c r="H97" s="27">
+        <v>5.0999999999999996</v>
       </c>
       <c r="I97" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J97" s="25" t="s">
-        <v>388</v>
+        <v>215</v>
+      </c>
+      <c r="J97" s="29" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>270</v>
+        <v>228</v>
       </c>
       <c r="C98" s="18" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="D98" s="18"/>
       <c r="E98" s="18"/>
       <c r="F98" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G98" s="18">
-        <v>600</v>
-      </c>
-      <c r="H98" s="28">
-        <v>4.4000000000000004</v>
+        <v>1050</v>
+      </c>
+      <c r="H98" s="27">
+        <v>5.0999999999999996</v>
       </c>
       <c r="I98" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J98" s="25" t="s">
-        <v>388</v>
+        <v>215</v>
+      </c>
+      <c r="J98" s="29" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="C99" s="18" t="s">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="D99" s="18"/>
       <c r="E99" s="18"/>
       <c r="F99" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G99" s="18">
-        <v>200</v>
-      </c>
-      <c r="H99" s="28">
-        <v>7.6</v>
+        <v>600</v>
+      </c>
+      <c r="H99" s="27">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I99" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="J99" s="25" t="s">
-        <v>425</v>
+        <v>215</v>
+      </c>
+      <c r="J99" s="29" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>280</v>
+        <v>231</v>
       </c>
       <c r="D100" s="18"/>
       <c r="E100" s="18"/>
       <c r="F100" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G100" s="18">
-        <v>200</v>
-      </c>
-      <c r="H100" s="28">
-        <v>7</v>
+        <v>600</v>
+      </c>
+      <c r="H100" s="27">
+        <v>4.4000000000000004</v>
       </c>
       <c r="I100" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="J100" s="25" t="s">
-        <v>425</v>
+        <v>215</v>
+      </c>
+      <c r="J100" s="29" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="D101" s="18"/>
       <c r="E101" s="18"/>
       <c r="F101" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G101" s="18">
-        <v>750</v>
-      </c>
-      <c r="H101" s="28">
-        <v>6.5</v>
+        <v>200</v>
+      </c>
+      <c r="H101" s="27">
+        <v>7.6</v>
       </c>
       <c r="I101" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="J101" s="25" t="s">
-        <v>430</v>
+        <v>216</v>
+      </c>
+      <c r="J101" s="29" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="C102" s="18" t="s">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="D102" s="18"/>
       <c r="E102" s="18"/>
       <c r="F102" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G102" s="18">
-        <v>750</v>
-      </c>
-      <c r="H102" s="28">
-        <v>6.55</v>
+        <v>200</v>
+      </c>
+      <c r="H102" s="27">
+        <v>7</v>
       </c>
       <c r="I102" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="J102" s="25" t="s">
-        <v>442</v>
+        <v>216</v>
+      </c>
+      <c r="J102" s="29" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="D103" s="18"/>
       <c r="E103" s="18"/>
       <c r="F103" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G103" s="18">
-        <v>600</v>
-      </c>
-      <c r="H103" s="28">
-        <v>5.65</v>
+        <v>750</v>
+      </c>
+      <c r="H103" s="27">
+        <v>6.5</v>
       </c>
       <c r="I103" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J103" s="25" t="s">
-        <v>388</v>
+        <v>216</v>
+      </c>
+      <c r="J103" s="29" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>284</v>
+        <v>241</v>
       </c>
       <c r="C104" s="18" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="D104" s="18"/>
       <c r="E104" s="18"/>
       <c r="F104" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G104" s="18">
-        <v>700</v>
-      </c>
-      <c r="H104" s="28">
-        <v>5.95</v>
+        <v>750</v>
+      </c>
+      <c r="H104" s="27">
+        <v>6.55</v>
       </c>
       <c r="I104" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="J104" s="25" t="s">
-        <v>426</v>
+        <v>216</v>
+      </c>
+      <c r="J104" s="29" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
       <c r="D105" s="18"/>
       <c r="E105" s="18"/>
       <c r="F105" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G105" s="18">
-        <v>50</v>
-      </c>
-      <c r="H105" s="28">
-        <v>13.3</v>
+        <v>600</v>
+      </c>
+      <c r="H105" s="27">
+        <v>5.65</v>
       </c>
       <c r="I105" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="J105" s="25" t="s">
-        <v>380</v>
+        <v>215</v>
+      </c>
+      <c r="J105" s="29" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>324</v>
+        <v>247</v>
       </c>
       <c r="D106" s="18"/>
       <c r="E106" s="18"/>
       <c r="F106" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G106" s="18">
-        <v>50</v>
-      </c>
-      <c r="H106" s="28">
-        <v>12</v>
+        <v>700</v>
+      </c>
+      <c r="H106" s="27">
+        <v>5.95</v>
       </c>
       <c r="I106" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="J106" s="25" t="s">
-        <v>380</v>
+        <v>215</v>
+      </c>
+      <c r="J106" s="29" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="C107" s="18" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="D107" s="18"/>
       <c r="E107" s="18"/>
       <c r="F107" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G107" s="18">
         <v>50</v>
       </c>
-      <c r="H107" s="28">
+      <c r="H107" s="27">
         <v>13.3</v>
       </c>
       <c r="I107" s="18" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="J107" s="25" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B108" s="18" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="C108" s="18" t="s">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
       <c r="F108" s="18" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G108" s="18">
         <v>50</v>
       </c>
-      <c r="H108" s="28">
+      <c r="H108" s="27">
         <v>12</v>
       </c>
       <c r="I108" s="18" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="J108" s="25" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="C109" s="18" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="D109" s="18"/>
       <c r="E109" s="18"/>
       <c r="F109" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G109" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="H109" s="28">
+        <v>76</v>
+      </c>
+      <c r="G109" s="18">
+        <v>50</v>
+      </c>
+      <c r="H109" s="27">
         <v>13.3</v>
       </c>
       <c r="I109" s="18" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="J109" s="25" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B110" s="18" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="C110" s="18" t="s">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="D110" s="18"/>
       <c r="E110" s="18"/>
       <c r="F110" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G110" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="H110" s="28">
+        <v>76</v>
+      </c>
+      <c r="G110" s="18">
+        <v>50</v>
+      </c>
+      <c r="H110" s="27">
         <v>12</v>
       </c>
       <c r="I110" s="18" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="J110" s="25" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="25"/>
+      <c r="A111" s="25" t="s">
+        <v>77</v>
+      </c>
       <c r="B111" s="18" t="s">
-        <v>68</v>
+        <v>252</v>
       </c>
       <c r="C111" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E111" s="18" t="s">
-        <v>68</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
       <c r="F111" s="18" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H111" s="18" t="s">
-        <v>68</v>
+        <v>149</v>
+      </c>
+      <c r="H111" s="27">
+        <v>13.3</v>
       </c>
       <c r="I111" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J111" s="18" t="s">
-        <v>68</v>
+        <v>329</v>
+      </c>
+      <c r="J111" s="25" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="25"/>
+      <c r="A112" s="25" t="s">
+        <v>77</v>
+      </c>
       <c r="B112" s="18" t="s">
-        <v>68</v>
+        <v>253</v>
       </c>
       <c r="C112" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E112" s="18" t="s">
-        <v>68</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
       <c r="F112" s="18" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H112" s="18" t="s">
-        <v>68</v>
+        <v>149</v>
+      </c>
+      <c r="H112" s="27">
+        <v>12</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J112" s="18" t="s">
-        <v>68</v>
+        <v>329</v>
+      </c>
+      <c r="J112" s="25" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="20"/>
-      <c r="D113" s="20"/>
-      <c r="E113" s="20"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
-      <c r="J113" s="21"/>
+      <c r="A113" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G113" s="18">
+        <v>100</v>
+      </c>
+      <c r="H113" s="27">
+        <v>15.8</v>
+      </c>
+      <c r="I113" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="J113" s="25" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>198</v>
+        <v>421</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>160</v>
+        <v>423</v>
       </c>
       <c r="D114" s="18"/>
       <c r="E114" s="18"/>
       <c r="F114" s="18" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="G114" s="18">
-        <v>300</v>
-      </c>
-      <c r="H114" s="18" t="s">
-        <v>164</v>
+        <v>100</v>
+      </c>
+      <c r="H114" s="27">
+        <v>16.8</v>
       </c>
       <c r="I114" s="18" t="s">
-        <v>163</v>
+        <v>329</v>
       </c>
       <c r="J114" s="25" t="s">
-        <v>217</v>
+        <v>532</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>197</v>
+        <v>439</v>
       </c>
       <c r="C115" s="18" t="s">
-        <v>161</v>
+        <v>440</v>
       </c>
       <c r="D115" s="18"/>
       <c r="E115" s="18"/>
       <c r="F115" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G115" s="18">
-        <v>300</v>
-      </c>
-      <c r="H115" s="18" t="s">
-        <v>165</v>
+        <v>76</v>
+      </c>
+      <c r="G115" s="18"/>
+      <c r="H115" s="27">
+        <v>8.75</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>163</v>
+        <v>71</v>
       </c>
       <c r="J115" s="25" t="s">
-        <v>217</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="25" t="s">
-        <v>95</v>
-      </c>
+      <c r="A116" s="25"/>
       <c r="B116" s="18" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="C116" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="D116" s="18"/>
-      <c r="E116" s="18"/>
+        <v>68</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E116" s="18" t="s">
+        <v>68</v>
+      </c>
       <c r="F116" s="18" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>169</v>
+        <v>68</v>
       </c>
       <c r="I116" s="18" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="J116" s="18" t="s">
-        <v>190</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="25" t="s">
-        <v>95</v>
-      </c>
+      <c r="A117" s="25"/>
       <c r="B117" s="18" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="C117" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18"/>
+        <v>68</v>
+      </c>
+      <c r="D117" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E117" s="18" t="s">
+        <v>68</v>
+      </c>
       <c r="F117" s="18" t="s">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>227</v>
+        <v>68</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="J117" s="18" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B118" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C118" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="D118" s="18"/>
-      <c r="E118" s="18"/>
-      <c r="F118" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G118" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="H118" s="18"/>
-      <c r="I118" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="J118" s="18" t="s">
-        <v>186</v>
-      </c>
+      <c r="A118" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="20"/>
+      <c r="D118" s="20"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="20"/>
+      <c r="I118" s="20"/>
+      <c r="J118" s="21"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="D119" s="18"/>
       <c r="E119" s="18"/>
       <c r="F119" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G119" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H119" s="18"/>
+        <v>143</v>
+      </c>
+      <c r="G119" s="18">
+        <v>300</v>
+      </c>
+      <c r="H119" s="18" t="s">
+        <v>145</v>
+      </c>
       <c r="I119" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="J119" s="18" t="s">
-        <v>187</v>
+        <v>144</v>
+      </c>
+      <c r="J119" s="25" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B120" s="18" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="D120" s="18"/>
       <c r="E120" s="18"/>
       <c r="F120" s="18" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G120" s="18">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="J120" s="18" t="s">
-        <v>221</v>
+        <v>144</v>
+      </c>
+      <c r="J120" s="25" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="D121" s="18"/>
       <c r="E121" s="18"/>
       <c r="F121" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G121" s="18">
-        <v>25</v>
+        <v>143</v>
+      </c>
+      <c r="G121" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="H121" s="18" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="I121" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="J121" s="18" t="s">
-        <v>221</v>
+        <v>87</v>
+      </c>
+      <c r="J121" s="30" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B122" s="18" t="s">
-        <v>228</v>
+        <v>151</v>
       </c>
       <c r="C122" s="18" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="D122" s="18"/>
       <c r="E122" s="18"/>
       <c r="F122" s="18" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G122" s="18" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="H122" s="18" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="I122" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J122" s="18" t="s">
-        <v>221</v>
+        <v>74</v>
+      </c>
+      <c r="J122" s="30" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="C123" s="18" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="D123" s="18"/>
       <c r="E123" s="18"/>
       <c r="F123" s="18" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="H123" s="18" t="s">
-        <v>234</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="H123" s="18"/>
       <c r="I123" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J123" s="18" t="s">
-        <v>221</v>
+        <v>166</v>
+      </c>
+      <c r="J123" s="30" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B124" s="18" t="s">
-        <v>239</v>
+        <v>163</v>
       </c>
       <c r="C124" s="18" t="s">
-        <v>241</v>
+        <v>164</v>
       </c>
       <c r="D124" s="18"/>
       <c r="E124" s="18"/>
       <c r="F124" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G124" s="18">
-        <v>25</v>
-      </c>
-      <c r="H124" s="18" t="s">
-        <v>234</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="G124" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="H124" s="18"/>
       <c r="I124" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="J124" s="18" t="s">
-        <v>221</v>
+        <v>166</v>
+      </c>
+      <c r="J124" s="30" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>240</v>
+        <v>169</v>
       </c>
       <c r="C125" s="18" t="s">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="D125" s="18"/>
       <c r="E125" s="18"/>
       <c r="F125" s="18" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G125" s="18">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>244</v>
+        <v>194</v>
       </c>
       <c r="I125" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="J125" s="18" t="s">
-        <v>221</v>
+        <v>88</v>
+      </c>
+      <c r="J125" s="30" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B126" s="18" t="s">
-        <v>258</v>
+        <v>170</v>
       </c>
       <c r="C126" s="18" t="s">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="D126" s="18"/>
       <c r="E126" s="18"/>
       <c r="F126" s="18" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="G126" s="18">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="I126" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J126" s="18" t="s">
-        <v>221</v>
+        <v>90</v>
+      </c>
+      <c r="J126" s="30" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="25" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>259</v>
+        <v>196</v>
       </c>
       <c r="C127" s="18" t="s">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="D127" s="18"/>
       <c r="E127" s="18"/>
       <c r="F127" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G127" s="18">
+        <v>143</v>
+      </c>
+      <c r="G127" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H127" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="I127" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J127" s="30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B128" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C128" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G128" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="H128" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="I128" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J128" s="30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B129" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C129" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G129" s="18">
+        <v>25</v>
+      </c>
+      <c r="H129" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="I129" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J129" s="30" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B130" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C130" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D130" s="18"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G130" s="18">
+        <v>20</v>
+      </c>
+      <c r="H130" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="I130" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J130" s="30" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C131" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G131" s="18">
         <v>50</v>
       </c>
-      <c r="H127" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="I127" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="J127" s="18" t="s">
+      <c r="H131" s="18" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="25"/>
-      <c r="B128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I128" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J128" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="25"/>
-      <c r="B129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I129" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J129" s="18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I130" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="J130" s="18" t="s">
+      <c r="I131" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J131" s="30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B132" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C132" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G132" s="18">
+        <v>50</v>
+      </c>
+      <c r="H132" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="I132" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="J132" s="30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G133" s="18">
+        <v>50</v>
+      </c>
+      <c r="H133" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="I133" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J133" s="30" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" s="25"/>
+      <c r="B134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I134" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J134" s="18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I135" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J135" s="18" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J132" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:J137" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
 </worksheet>
